--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -222,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I17" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:I17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I14" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:I14"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Excesos" dataDxfId="0"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O41" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:O41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O57" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:O57"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Conductor"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H76" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:H76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H165" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:H165"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Secuencial" dataDxfId="0"/>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/09/17 23:59:59</t>
+          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/09/26 23:59:59</t>
         </is>
       </c>
     </row>
@@ -647,26 +647,26 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.008483796296296297</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.001696759259259259</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1.6</v>
+        <v>20.4</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>101.6</v>
+        <v>113.9</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>101.6</v>
+        <v>103.1</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -678,26 +678,26 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.01055555555555556</v>
+        <v>0.003472222222222222</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.0006597222222222222</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>23.7</v>
+        <v>7.3</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>110.7</v>
+        <v>103.4</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>104</v>
+        <v>101.5</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
@@ -709,26 +709,26 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.002638888888888889</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0004398148148148148</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>102</v>
+        <v>107.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>102</v>
+        <v>103.6</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>0</v>
@@ -740,26 +740,26 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GV TM5 RXXG-15 E CABANILLA</t>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0008912037037037037</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0004456018518518519</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>101.7</v>
+        <v>102.5</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>101.7</v>
+        <v>101.9</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -771,26 +771,26 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.0007175925925925926</v>
+        <v>0.000474537037037037</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.0003587962962962963</v>
+        <v>0.000474537037037037</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>107.7</v>
+        <v>100.6</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>103.9</v>
+        <v>100.6</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
@@ -802,26 +802,26 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.001747685185185185</v>
+        <v>0.03969907407407407</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.0005825578703703703</v>
+        <v>0.001890428240740741</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>3.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>111.6</v>
+        <v>101.7</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>105.1</v>
+        <v>100.6</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
@@ -833,26 +833,26 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GP DONGFENG DF6-RXDL-60</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.001388888888888889</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0.000462962962962963</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>102.4</v>
+        <v>103.6</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>101.3</v>
+        <v>103.6</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
@@ -864,26 +864,26 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>0.0006828703703703704</v>
+        <v>0.0006597222222222222</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>0.0006828703703703704</v>
+        <v>0.0003298611111111111</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>100.4</v>
+        <v>101</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>100.4</v>
+        <v>100.6</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>0</v>
@@ -895,124 +895,31 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>0.002083333333333333</v>
+        <v>0.01033564814814815</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.001148402777777778</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>4.1</v>
+        <v>24.2</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>107.3</v>
+        <v>106.9</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>105.6</v>
+        <v>102</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0.001365740740740741</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>0.0004552430555555555</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>0.0006944444444444445</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>0.0006944444444444445</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>GV TOLVA SPGW-29 V OLIVARES</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>0.0006828703703703704</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>0.0006828703703703704</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1037,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O347"/>
+  <dimension ref="A1:O392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -1065,7 +972,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/07 00:00:00 Hasta: 2026/09/13 23:59:58</t>
+          <t>Desde : 2026/09/14 00:00:00 Hasta: 2026/09/20 23:59:58</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15818,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
         <v>1</v>
       </c>
@@ -15970,7 +15876,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
         <v>2</v>
       </c>
@@ -16029,7 +15934,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
         <v>3</v>
       </c>
@@ -16088,7 +15992,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
         <v>1</v>
       </c>
@@ -16147,7 +16050,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
         <v>4</v>
       </c>
@@ -16206,7 +16108,6 @@
           <t>GV TOLVA SPGW-29 V OLIVARES</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr"/>
       <c r="C265" t="n">
         <v>1</v>
       </c>
@@ -16265,7 +16166,6 @@
           <t>GP DONGFENG DF6-RXDL-60</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
         <v>1</v>
       </c>
@@ -16324,7 +16224,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
         <v>5</v>
       </c>
@@ -16383,7 +16282,6 @@
           <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
       <c r="C268" t="n">
         <v>1</v>
       </c>
@@ -16442,7 +16340,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
         <v>1</v>
       </c>
@@ -16501,7 +16398,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
         <v>6</v>
       </c>
@@ -16560,7 +16456,6 @@
           <t>GP DONGFENG DF6-RXDL-60</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
       <c r="C271" t="n">
         <v>2</v>
       </c>
@@ -16619,7 +16514,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
         <v>7</v>
       </c>
@@ -16678,7 +16572,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
         <v>2</v>
       </c>
@@ -16737,7 +16630,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
         <v>8</v>
       </c>
@@ -16796,7 +16688,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
         <v>9</v>
       </c>
@@ -16855,7 +16746,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
         <v>10</v>
       </c>
@@ -16914,7 +16804,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr"/>
       <c r="C277" t="n">
         <v>11</v>
       </c>
@@ -16973,7 +16862,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
         <v>12</v>
       </c>
@@ -17032,7 +16920,6 @@
           <t>GV SHLC-74 B MIRANDA</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
         <v>1</v>
       </c>
@@ -17091,7 +16978,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
         <v>3</v>
       </c>
@@ -17150,7 +17036,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
         <v>1</v>
       </c>
@@ -17209,7 +17094,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr"/>
       <c r="C282" t="n">
         <v>1</v>
       </c>
@@ -17268,7 +17152,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr"/>
       <c r="C283" t="n">
         <v>13</v>
       </c>
@@ -17327,7 +17210,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr"/>
       <c r="C284" t="n">
         <v>14</v>
       </c>
@@ -17386,7 +17268,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
         <v>1</v>
       </c>
@@ -17447,7 +17328,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr"/>
       <c r="C286" t="n">
         <v>2</v>
       </c>
@@ -17506,7 +17386,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
         <v>1</v>
       </c>
@@ -17565,7 +17444,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
         <v>15</v>
       </c>
@@ -17624,7 +17502,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
         <v>1</v>
       </c>
@@ -17683,7 +17560,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr"/>
       <c r="C290" t="n">
         <v>16</v>
       </c>
@@ -17742,7 +17618,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr"/>
       <c r="C291" t="n">
         <v>2</v>
       </c>
@@ -17801,7 +17676,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr"/>
       <c r="C292" t="n">
         <v>3</v>
       </c>
@@ -17860,7 +17734,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr"/>
       <c r="C293" t="n">
         <v>2</v>
       </c>
@@ -17919,7 +17792,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr"/>
       <c r="C294" t="n">
         <v>3</v>
       </c>
@@ -17978,7 +17850,6 @@
           <t>GP DONGFENG DF6-RXDL-60</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr"/>
       <c r="C295" t="n">
         <v>3</v>
       </c>
@@ -18037,7 +17908,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr"/>
       <c r="C296" t="n">
         <v>1</v>
       </c>
@@ -18096,7 +17966,6 @@
           <t>GP DONGFENG DF6-RXDL-60</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr"/>
       <c r="C297" t="n">
         <v>1</v>
       </c>
@@ -18155,7 +18024,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr"/>
       <c r="C298" t="n">
         <v>1</v>
       </c>
@@ -18214,7 +18082,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr"/>
       <c r="C299" t="n">
         <v>1</v>
       </c>
@@ -18273,7 +18140,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
         <v>1</v>
       </c>
@@ -18332,7 +18198,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
         <v>2</v>
       </c>
@@ -18391,7 +18256,6 @@
           <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
         <v>1</v>
       </c>
@@ -18450,7 +18314,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>3</v>
       </c>
@@ -18509,7 +18372,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr"/>
       <c r="C304" t="n">
         <v>1</v>
       </c>
@@ -18568,7 +18430,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr"/>
       <c r="C305" t="n">
         <v>2</v>
       </c>
@@ -18627,7 +18488,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr"/>
       <c r="C306" t="n">
         <v>3</v>
       </c>
@@ -18686,7 +18546,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
         <v>1</v>
       </c>
@@ -18745,7 +18604,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
         <v>4</v>
       </c>
@@ -18804,7 +18662,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr"/>
       <c r="C309" t="n">
         <v>5</v>
       </c>
@@ -18863,7 +18720,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
         <v>6</v>
       </c>
@@ -18922,7 +18778,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr"/>
       <c r="C311" t="n">
         <v>7</v>
       </c>
@@ -18981,7 +18836,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
         <v>8</v>
       </c>
@@ -19040,7 +18894,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
         <v>4</v>
       </c>
@@ -19099,7 +18952,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
         <v>1</v>
       </c>
@@ -19158,7 +19010,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr"/>
       <c r="C315" t="n">
         <v>9</v>
       </c>
@@ -19217,7 +19068,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
         <v>2</v>
       </c>
@@ -19276,7 +19126,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
         <v>10</v>
       </c>
@@ -19335,7 +19184,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
         <v>3</v>
       </c>
@@ -19394,7 +19242,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr"/>
       <c r="C319" t="n">
         <v>11</v>
       </c>
@@ -19453,7 +19300,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
         <v>12</v>
       </c>
@@ -19512,7 +19358,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>13</v>
       </c>
@@ -19571,7 +19416,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr"/>
       <c r="C322" t="n">
         <v>14</v>
       </c>
@@ -19630,7 +19474,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr"/>
       <c r="C323" t="n">
         <v>15</v>
       </c>
@@ -19689,7 +19532,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
         <v>16</v>
       </c>
@@ -19748,7 +19590,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
         <v>17</v>
       </c>
@@ -19807,7 +19648,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
         <v>18</v>
       </c>
@@ -19866,7 +19706,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr"/>
       <c r="C327" t="n">
         <v>19</v>
       </c>
@@ -19925,7 +19764,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr"/>
       <c r="C328" t="n">
         <v>20</v>
       </c>
@@ -19984,7 +19822,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
         <v>21</v>
       </c>
@@ -20043,7 +19880,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr"/>
       <c r="C330" t="n">
         <v>4</v>
       </c>
@@ -20102,7 +19938,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr"/>
       <c r="C331" t="n">
         <v>5</v>
       </c>
@@ -20161,7 +19996,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr"/>
       <c r="C332" t="n">
         <v>2</v>
       </c>
@@ -20220,7 +20054,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
         <v>3</v>
       </c>
@@ -20279,7 +20112,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
         <v>2</v>
       </c>
@@ -20338,7 +20170,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr"/>
       <c r="C335" t="n">
         <v>4</v>
       </c>
@@ -20397,7 +20228,6 @@
           <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
         <v>5</v>
       </c>
@@ -20456,7 +20286,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
         <v>3</v>
       </c>
@@ -20515,7 +20344,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr"/>
       <c r="C338" t="n">
         <v>4</v>
       </c>
@@ -20574,7 +20402,6 @@
           <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
         <v>5</v>
       </c>
@@ -20633,7 +20460,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
         <v>6</v>
       </c>
@@ -20692,7 +20518,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
         <v>5</v>
       </c>
@@ -20751,7 +20576,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
         <v>6</v>
       </c>
@@ -20810,7 +20634,6 @@
           <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
         <v>2</v>
       </c>
@@ -20869,7 +20692,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
         <v>2</v>
       </c>
@@ -20928,7 +20750,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
         <v>7</v>
       </c>
@@ -20987,7 +20808,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
         <v>8</v>
       </c>
@@ -21046,7 +20866,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr"/>
       <c r="C347" t="n">
         <v>9</v>
       </c>
@@ -21096,6 +20915,2669 @@
         <v>0</v>
       </c>
       <c r="O347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" t="n">
+        <v>1</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2026/09/21 06:48:39</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-32.487837,-71.162004</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>2026/09/21 06:49:39</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-32.482624,-71.176619</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Avenida Humeres, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J348" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K348" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L348" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="M348" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="N348" t="n">
+        <v>0</v>
+      </c>
+      <c r="O348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="n">
+        <v>2</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026/09/21 12:06:37</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-32.573002,-71.291593</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Avenida Humeres, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2026/09/21 12:07:37</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-32.577297,-71.308318</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>s/n, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J349" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K349" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L349" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="M349" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="N349" t="n">
+        <v>0</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="n">
+        <v>1</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026/09/21 16:30:44</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-33.064531,-71.582122</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>2026/09/21 16:31:43</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-33.073399,-71.569769</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J350" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K350" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L350" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M350" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="N350" t="n">
+        <v>0</v>
+      </c>
+      <c r="O350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>DONGFENG DF6 SRSR-97</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="n">
+        <v>1</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026/09/22 05:25:50</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-33.16695,-71.530733</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2026/09/22 05:26:50</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-33.159275,-71.545768</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J351" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K351" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L351" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M351" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N351" t="n">
+        <v>0</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="n">
+        <v>2</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2026/09/22 06:52:22</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-33.106964,-71.550335</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>2026/09/22 06:52:42</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-33.108835,-71.556265</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J352" s="14" t="n">
+        <v>0.0002314814814814815</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L352" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="M352" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="N352" t="n">
+        <v>0</v>
+      </c>
+      <c r="O352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="n">
+        <v>3</v>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026/09/22 06:58:45</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-33.174097,-71.517021</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>2026/09/22 06:59:45</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-33.182965,-71.503923</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J353" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K353" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L353" t="n">
+        <v>103</v>
+      </c>
+      <c r="M353" t="n">
+        <v>103</v>
+      </c>
+      <c r="N353" t="n">
+        <v>0</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="n">
+        <v>1</v>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026/09/22 07:45:10</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-33.100187,-71.547878</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2026/09/22 07:45:36</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-33.095247,-71.543902</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J354" s="14" t="n">
+        <v>0.0003009259259259259</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L354" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="M354" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="N354" t="n">
+        <v>0</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="n">
+        <v>3</v>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026/09/22 16:59:18</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-32.402325,-71.369648</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>s/n, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>2026/09/22 17:01:36</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-32.420991,-71.336063</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Papudo, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J355" s="14" t="n">
+        <v>0.001597222222222222</v>
+      </c>
+      <c r="K355" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L355" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="M355" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="N355" t="n">
+        <v>0</v>
+      </c>
+      <c r="O355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="n">
+        <v>2</v>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026/09/22 20:35:30</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-33.07978,-71.626201</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>2026/09/22 20:36:02</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-33.074449,-71.627144</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J356" s="14" t="n">
+        <v>0.0003703703703703704</v>
+      </c>
+      <c r="K356" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L356" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M356" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N356" t="n">
+        <v>0</v>
+      </c>
+      <c r="O356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="n">
+        <v>3</v>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:09:48</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-33.07467,-71.627206</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:09:48</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-33.07467,-71.627206</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J357" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L357" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="M357" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="N357" t="n">
+        <v>0</v>
+      </c>
+      <c r="O357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="n">
+        <v>4</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:10:22</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-33.081773,-71.624192</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:10:41</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-33.083436,-71.619366</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J358" s="14" t="n">
+        <v>0.0002199074074074074</v>
+      </c>
+      <c r="K358" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L358" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="M358" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="N358" t="n">
+        <v>0</v>
+      </c>
+      <c r="O358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="n">
+        <v>5</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:12:11</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-33.093374,-71.603202</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:13:50</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-33.098312,-71.576965</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J359" s="14" t="n">
+        <v>0.001145833333333333</v>
+      </c>
+      <c r="K359" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L359" t="n">
+        <v>107</v>
+      </c>
+      <c r="M359" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="N359" t="n">
+        <v>0</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="n">
+        <v>6</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:15:50</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-33.108176,-71.555779</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:16:02</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-33.109708,-71.554261</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J360" s="14" t="n">
+        <v>0.0001388888888888889</v>
+      </c>
+      <c r="K360" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L360" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="M360" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="N360" t="n">
+        <v>0</v>
+      </c>
+      <c r="O360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="n">
+        <v>7</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:16:51</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-33.102198,-71.548</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:17:15</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-33.096372,-71.545629</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J361" s="14" t="n">
+        <v>0.0002777777777777778</v>
+      </c>
+      <c r="K361" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L361" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="M361" t="n">
+        <v>104</v>
+      </c>
+      <c r="N361" t="n">
+        <v>0</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="n">
+        <v>8</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:17:45</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-33.090113,-71.541609</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:18:40</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-33.07789,-71.54688</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J362" s="14" t="n">
+        <v>0.0006365740740740741</v>
+      </c>
+      <c r="K362" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L362" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="M362" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="N362" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="n">
+        <v>9</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:20:51</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-33.056024,-71.529652</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:21:04</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-33.052977,-71.529235</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J363" s="14" t="n">
+        <v>0.000150462962962963</v>
+      </c>
+      <c r="K363" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L363" t="n">
+        <v>102</v>
+      </c>
+      <c r="M363" t="n">
+        <v>102</v>
+      </c>
+      <c r="N363" t="n">
+        <v>0</v>
+      </c>
+      <c r="O363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="n">
+        <v>10</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:21:51</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-33.050259,-71.526545</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>2026/09/22 21:22:04</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-33.052978,-71.525812</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J364" s="14" t="n">
+        <v>0.000150462962962963</v>
+      </c>
+      <c r="K364" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L364" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="M364" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="N364" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="n">
+        <v>11</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026/09/22 22:52:53</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-33.080648,-71.5467</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>2026/09/22 22:53:54</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-33.094237,-71.542709</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J365" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K365" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L365" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="M365" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="N365" t="n">
+        <v>0</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="n">
+        <v>12</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026/09/22 23:00:53</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-33.080785,-71.625629</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2026/09/22 23:00:55</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-33.080376,-71.625952</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J366" s="14" t="n">
+        <v>2.314814814814815e-05</v>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L366" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M366" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N366" t="n">
+        <v>0</v>
+      </c>
+      <c r="O366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="n">
+        <v>1</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026/09/23 06:44:10</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-32.586372,-71.330742</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>2026/09/23 06:45:11</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-32.592754,-71.346296</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J367" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K367" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L367" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M367" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N367" t="n">
+        <v>0</v>
+      </c>
+      <c r="O367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="n">
+        <v>4</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026/09/23 06:47:44</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-33.106438,-71.549498</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>2026/09/23 06:48:23</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-33.110597,-71.559406</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J368" s="14" t="n">
+        <v>0.0004513888888888889</v>
+      </c>
+      <c r="K368" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L368" t="n">
+        <v>114</v>
+      </c>
+      <c r="M368" t="n">
+        <v>114</v>
+      </c>
+      <c r="N368" t="n">
+        <v>0</v>
+      </c>
+      <c r="O368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="n">
+        <v>5</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026/09/23 07:01:26</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-33.254285,-71.441848</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2026/09/23 07:01:53</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-33.259087,-71.438325</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Paso de Nivel Lo Vásquez, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J369" s="14" t="n">
+        <v>0.0003125</v>
+      </c>
+      <c r="K369" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L369" t="n">
+        <v>113</v>
+      </c>
+      <c r="M369" t="n">
+        <v>113</v>
+      </c>
+      <c r="N369" t="n">
+        <v>0</v>
+      </c>
+      <c r="O369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="n">
+        <v>4</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026/09/23 07:57:23</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-32.419658,-71.337312</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Papudo, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2026/09/23 07:58:22</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-32.409862,-71.34845</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J370" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K370" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L370" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="M370" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="N370" t="n">
+        <v>0</v>
+      </c>
+      <c r="O370" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="n">
+        <v>13</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026/09/23 16:22:13</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-33.067759,-71.633023</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>2026/09/23 16:22:39</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-33.072648,-71.627581</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J371" s="14" t="n">
+        <v>0.0003009259259259259</v>
+      </c>
+      <c r="K371" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L371" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="M371" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="N371" t="n">
+        <v>0</v>
+      </c>
+      <c r="O371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="n">
+        <v>14</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026/09/23 16:59:32</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-33.067309,-71.53576</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>2026/09/23 16:59:57</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-33.06375,-71.530232</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J372" s="14" t="n">
+        <v>0.0002893518518518518</v>
+      </c>
+      <c r="K372" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L372" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="M372" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="N372" t="n">
+        <v>0</v>
+      </c>
+      <c r="O372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>GV TOLVA SPGW-29 V OLIVARES</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="n">
+        <v>1</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026/09/23 17:35:53</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-32.801057,-71.44118</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2026/09/23 17:36:53</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-32.810575,-71.441477</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J373" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K373" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L373" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="M373" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="N373" t="n">
+        <v>0</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="n">
+        <v>1</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026/09/23 17:41:07</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-32.986627,-71.500563</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2026/09/23 17:42:07</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-32.972873,-71.499375</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J374" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K374" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L374" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="M374" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="N374" t="n">
+        <v>0</v>
+      </c>
+      <c r="O374" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="n">
+        <v>6</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026/09/24 06:55:05</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-33.170963,-71.523157</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Paso de Nivel Lo Vásquez, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>2026/09/24 06:56:05</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-33.178557,-71.508373</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J375" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K375" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L375" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="M375" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="N375" t="n">
+        <v>0</v>
+      </c>
+      <c r="O375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="n">
+        <v>1</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026/09/24 08:59:37</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-32.739544,-71.198615</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:00:37</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-32.752198,-71.196065</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J376" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K376" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L376" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="M376" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="N376" t="n">
+        <v>0</v>
+      </c>
+      <c r="O376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="n">
+        <v>2</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:09:37</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-32.83366,-71.220176</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:10:37</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-32.848271,-71.224416</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J377" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K377" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L377" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M377" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N377" t="n">
+        <v>0</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="n">
+        <v>3</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:11:37</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-32.863138,-71.226828</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:11:37</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-32.863138,-71.226828</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J378" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L378" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M378" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N378" t="n">
+        <v>0</v>
+      </c>
+      <c r="O378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="n">
+        <v>4</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:12:37</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-32.877664,-71.231555</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:14:37</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>-32.901562,-71.24669</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J379" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K379" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L379" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="M379" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="N379" t="n">
+        <v>0</v>
+      </c>
+      <c r="O379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="n">
+        <v>5</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:15:37</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-32.906838,-71.263422</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:15:37</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>-32.906838,-71.263422</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J380" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L380" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M380" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N380" t="n">
+        <v>0</v>
+      </c>
+      <c r="O380" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" t="n">
+        <v>6</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:16:37</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-32.917581,-71.275583</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:17:53</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-32.932927,-71.288722</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J381" s="14" t="n">
+        <v>0.0008796296296296296</v>
+      </c>
+      <c r="K381" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L381" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="M381" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N381" t="n">
+        <v>0</v>
+      </c>
+      <c r="O381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+      <c r="C382" t="n">
+        <v>7</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:28:37</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-33.051079,-71.331664</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2026/09/24 09:29:37</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-33.06071,-71.343696</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J382" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K382" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L382" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="M382" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="N382" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" t="n">
+        <v>1</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026/09/24 10:17:48</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-33.103997,-71.548121</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2026/09/24 10:18:21</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>-33.096468,-71.545796</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J383" s="14" t="n">
+        <v>0.0003819444444444445</v>
+      </c>
+      <c r="K383" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L383" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="M383" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="N383" t="n">
+        <v>0</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="n">
+        <v>2</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026/09/24 11:04:51</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-32.74668,-71.418272</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>2026/09/24 11:05:39</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>-32.736764,-71.417754</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J384" s="14" t="n">
+        <v>0.0005555555555555556</v>
+      </c>
+      <c r="K384" t="n">
+        <v>1</v>
+      </c>
+      <c r="L384" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M384" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N384" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="n">
+        <v>3</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:27:11</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-32.697632,-71.434125</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:28:11</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>-32.711743,-71.439001</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J385" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K385" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L385" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M385" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="n">
+        <v>4</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:30:11</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-32.736397,-71.430255</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>2026/09/24 14:31:07</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>-32.73887,-71.417684</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J386" s="14" t="n">
+        <v>0.0006481481481481481</v>
+      </c>
+      <c r="K386" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L386" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="M386" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="N386" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" t="n">
+        <v>5</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:17:42</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-33.106519,-71.549636</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2026/09/24 15:18:16</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>-33.109626,-71.558333</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J387" s="14" t="n">
+        <v>0.0003935185185185185</v>
+      </c>
+      <c r="K387" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L387" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="M387" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="N387" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="n">
+        <v>6</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026/09/24 16:03:25</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-33.225873,-71.408757</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2026/09/24 16:03:43</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>-33.226252,-71.403608</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J388" s="14" t="n">
+        <v>0.0002083333333333333</v>
+      </c>
+      <c r="K388" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L388" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="M388" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="N388" t="n">
+        <v>0</v>
+      </c>
+      <c r="O388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="n">
+        <v>7</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026/09/24 16:07:24</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-33.259735,-71.437511</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2026/09/24 16:08:24</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>-33.247305,-71.447136</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J389" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K389" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L389" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="M389" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0</v>
+      </c>
+      <c r="O389" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="n">
+        <v>8</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026/09/24 16:17:24</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-33.158164,-71.548034</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2026/09/24 16:18:24</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>-33.148261,-71.559017</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J390" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K390" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L390" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="M390" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0</v>
+      </c>
+      <c r="O390" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>DONGFENG DF6 SRSR-97</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="n">
+        <v>2</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026/09/24 16:50:40</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-33.173599,-71.518062</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2026/09/24 16:51:40</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-33.182621,-71.504213</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J391" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K391" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L391" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="M391" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="n">
+        <v>15</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026/09/26 05:57:45</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-33.090501,-71.541783</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2026/09/26 05:58:06</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-33.094862,-71.543568</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J392" s="14" t="n">
+        <v>0.0002430555555555555</v>
+      </c>
+      <c r="K392" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L392" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="M392" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="N392" t="n">
+        <v>0</v>
+      </c>
+      <c r="O392" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21120,7 +23602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -21146,7 +23628,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/07 00:00:00 Hasta: 2026/09/13 23:59:58</t>
+          <t>Desde : 2026/09/14 00:00:00 Hasta: 2026/09/20 23:59:58</t>
         </is>
       </c>
     </row>
@@ -21195,7 +23677,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -21203,33 +23685,33 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 16:22:38</t>
+          <t>2026/09/14 11:35:40</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-33.340314,-71.366758</t>
+          <t>-33.096592,-71.546281</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>101.6</v>
+        <v>100.3</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>83760.10000000001</v>
+        <v>63880.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>273.6</v>
+        <v>314.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
@@ -21237,101 +23719,101 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 16:23:38</t>
+          <t>2026/09/14 11:35:54</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>-33.333625,-71.381621</t>
+          <t>-33.098578,-71.548812</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>92.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>83761.7</v>
+        <v>63880.9</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>266.4</v>
+        <v>328.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 06:45:03</t>
+          <t>2026/09/16 15:01:00</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-33.141115,-71.562591</t>
+          <t>-33.167229,-71.530493</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>102.4</v>
+        <v>111.4</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>193016.7</v>
+        <v>64193.3</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>330.6</v>
+        <v>344.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 06:46:03</t>
+          <t>2026/09/16 15:02:00</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>-33.154084,-71.555717</t>
+          <t>-33.1753,-71.514666</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>94.7</v>
+        <v>101.7</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>193018.2</v>
+        <v>64195</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>356.9</v>
+        <v>349.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -21339,12 +23821,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 08:28:37</t>
+          <t>2026/09/16 15:03:00</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-33.189897,-71.498359</t>
+          <t>-33.186116,-71.501403</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -21353,19 +23835,19 @@
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>105.7</v>
+        <v>105</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>193066.8</v>
+        <v>64196.8</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>357.1</v>
+        <v>351.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
@@ -21373,12 +23855,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 08:29:37</t>
+          <t>2026/09/16 15:04:00</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-33.20141,-71.488764</t>
+          <t>-33.199588,-71.490643</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -21387,32 +23869,32 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>94.40000000000001</v>
+        <v>106.8</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>193068.4</v>
+        <v>64198.6</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>385.8</v>
+        <v>376.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 08:32:37</t>
+          <t>2026/09/16 15:05:00</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-33.236576,-71.459738</t>
+          <t>-33.210571,-71.478795</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -21421,32 +23903,32 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>108.7</v>
+        <v>113.9</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>193073.2</v>
+        <v>64200.2</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>325.1</v>
+        <v>357.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 08:33:37</t>
+          <t>2026/09/16 15:06:00</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>-33.246908,-71.447579</t>
+          <t>-33.225062,-71.468933</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -21455,134 +23937,134 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>95.2</v>
+        <v>111</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>193074.8</v>
+        <v>64202.1</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>265.9</v>
+        <v>325.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 16:22:13</t>
+          <t>2026/09/16 15:07:00</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-33.202891,-71.487012</t>
+          <t>-33.237036,-71.459138</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>103.7</v>
+        <v>106.2</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>193209.6</v>
+        <v>64203.7</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>392.8</v>
+        <v>317.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 16:23:13</t>
+          <t>2026/09/16 15:08:00</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-33.191056,-71.497234</t>
+          <t>-33.249098,-71.445932</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>92.7</v>
+        <v>105.8</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>193211.2</v>
+        <v>64205.5</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>361.8</v>
+        <v>261.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 16:01:03</t>
+          <t>2026/09/16 15:08:59</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-33.263706,-71.434921</t>
+          <t>-33.259158,-71.438359</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Paso de Nivel Lo Vásquez, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>110.7</v>
+        <v>24.2</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>193426.4</v>
+        <v>64206.8</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>288.3</v>
+        <v>275.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 16:02:03</t>
+          <t>2026/09/16 15:42:37</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>-33.250958,-71.444248</t>
+          <t>-33.221243,-71.470765</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -21591,134 +24073,134 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>94.09999999999999</v>
+        <v>101.9</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>193428.1</v>
+        <v>64214.9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>264.2</v>
+        <v>333.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 17:19:27</t>
+          <t>2026/09/16 15:43:37</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-33.164158,-71.536312</t>
+          <t>-33.209398,-71.479899</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>100.2</v>
+        <v>90.5</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>193504.6</v>
+        <v>64216.4</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>356.2</v>
+        <v>372.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 17:20:27</t>
+          <t>2026/09/16 15:44:37</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>-33.156574,-71.551051</t>
+          <t>-33.198486,-71.49131</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>94.09999999999999</v>
+        <v>100.2</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>193506.2</v>
+        <v>64218.1</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>361.2</v>
+        <v>372.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 06:53:51</t>
+          <t>2026/09/16 15:45:37</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-33.11288,-71.560133</t>
+          <t>-33.18722,-71.500328</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>102.5</v>
+        <v>82.3</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>193559</v>
+        <v>64219.6</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>343.8</v>
+        <v>355.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 06:54:50</t>
+          <t>2026/09/16 16:01:37</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>-33.127103,-71.561758</t>
+          <t>-33.141488,-71.562336</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -21727,421 +24209,421 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>94.40000000000001</v>
+        <v>101.8</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>193560.6</v>
+        <v>64227.4</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>338.9</v>
+        <v>336.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 10:06:02</t>
+          <t>2026/09/16 16:02:37</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-33.222265,-71.470266</t>
+          <t>-33.126063,-71.561539</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>102.4</v>
+        <v>109.1</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>193659.6</v>
+        <v>64229.1</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>326.5</v>
+        <v>339.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP SSZD-71  J VALLEJOS</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 10:07:02</t>
+          <t>2026/09/16 16:03:37</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>-33.210043,-71.479185</t>
+          <t>-33.110375,-71.55904</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>94.8</v>
+        <v>91.7</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>193661.2</v>
+        <v>64230.9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>366.1</v>
+        <v>344.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 10:08:02</t>
+          <t>2026/09/15 14:27:50</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-33.198948,-71.490923</t>
+          <t>-33.220359,-71.391567</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>101.7</v>
+        <v>101.9</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>193662.9</v>
+        <v>84090.10000000001</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>375.6</v>
+        <v>308.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 10:09:02</t>
+          <t>2026/09/15 14:28:50</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>-33.18709,-71.500413</t>
+          <t>-33.207985,-71.385576</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>91.8</v>
+        <v>92.3</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>193664.5</v>
+        <v>84091.60000000001</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>353.5</v>
+        <v>317.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 10:55:05</t>
+          <t>2026/09/16 07:25:22</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-32.943812,-71.513465</t>
+          <t>-33.157629,-71.548991</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>193721.1</v>
+        <v>84169</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>122.9</v>
+        <v>370.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 10:56:05</t>
+          <t>2026/09/16 07:26:22</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>-32.930068,-71.512177</t>
+          <t>-33.147258,-71.559468</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>92.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>193722.6</v>
+        <v>84170.5</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>49.9</v>
+        <v>341.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 12:00:05</t>
+          <t>2026/09/16 08:23:38</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-33.206795,-71.482856</t>
+          <t>-32.886351,-71.453382</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>109.9</v>
+        <v>100.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>193790.2</v>
+        <v>84216.8</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>390.9</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 12:01:05</t>
+          <t>2026/09/16 08:24:38</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>-33.218721,-71.472248</t>
+          <t>-32.875885,-71.455694</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>95.09999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>193791.9</v>
+        <v>84218</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>332.9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 12:03:05</t>
+          <t>2026/09/16 15:20:42</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>-33.241379,-71.452602</t>
+          <t>-33.169856,-71.525302</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>109.3</v>
+        <v>103.4</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>193795.1</v>
+        <v>84466.10000000001</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>290.5</v>
+        <v>347.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 12:04:05</t>
+          <t>2026/09/16 15:21:42</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>-33.253281,-71.442636</t>
+          <t>-33.176949,-71.511477</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>95</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>193796.7</v>
+        <v>84467.60000000001</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>261.4</v>
+        <v>347.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 07:50:42</t>
+          <t>2026/09/16 15:26:42</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-32.965085,-71.292094</t>
+          <t>-33.234051,-71.462338</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
         <v>100.8</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>193931.6</v>
+        <v>84475.5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>134</v>
+        <v>337.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TDLD-98 J PACHECHO</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 07:50:55</t>
+          <t>2026/09/16 15:27:42</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>-32.966022,-71.295684</t>
+          <t>-33.244005,-71.449885</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Limache, Marga Marga, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>93.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>193931.9</v>
+        <v>84477.10000000001</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>116.5</v>
+        <v>267.9</v>
       </c>
     </row>
     <row r="34">
@@ -22151,31 +24633,31 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 07:58:55</t>
+          <t>2026/09/14 13:37:23</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-33.055802,-71.337934</t>
+          <t>-33.102549,-71.548051</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>193944.7</v>
+        <v>194468.2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>185.3</v>
+        <v>344.1</v>
       </c>
     </row>
     <row r="35">
@@ -22185,31 +24667,31 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 07:59:55</t>
+          <t>2026/09/14 13:37:48</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>-33.065143,-71.350673</t>
+          <t>-33.09657,-71.545933</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>94.09999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>193946.2</v>
+        <v>194468.8</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>212.6</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36">
@@ -22219,31 +24701,31 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 16:10:39</t>
+          <t>2026/09/14 13:38:22</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>-33.312359,-71.404732</t>
+          <t>-33.089883,-71.541658</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>103.6</v>
+        <v>100.2</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>194059.6</v>
+        <v>194469.7</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>260.5</v>
+        <v>321.1</v>
       </c>
     </row>
     <row r="37">
@@ -22253,31 +24735,31 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 16:11:39</t>
+          <t>2026/09/14 13:38:23</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>-33.303287,-71.409927</t>
+          <t>-33.089633,-71.54168</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>77.09999999999999</v>
+        <v>100.1</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>194060.7</v>
+        <v>194469.8</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>257.8</v>
+        <v>322.3</v>
       </c>
     </row>
     <row r="38">
@@ -22287,31 +24769,31 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 06:58:57</t>
+          <t>2026/09/14 13:39:23</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>-33.182315,-71.504406</t>
+          <t>-33.078859,-71.546943</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>100.8</v>
+        <v>44.8</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>194147.7</v>
+        <v>194471.1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>346.2</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39">
@@ -22321,275 +24803,275 @@
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 06:59:57</t>
+          <t>2026/09/14 16:20:08</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>-33.194277,-71.494876</t>
+          <t>-33.124523,-71.56142</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>96.2</v>
+        <v>104.3</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>194149.3</v>
+        <v>194616.5</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>364.2</v>
+        <v>339.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 13:08:19</t>
+          <t>2026/09/14 16:21:08</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>-33.246608,-71.447616</t>
+          <t>-33.139039,-71.562985</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>102</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>127525.4</v>
+        <v>194618.1</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>266</v>
+        <v>332.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>GV SHLC-74 B MIRANDA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 13:09:19</t>
+          <t>2026/09/15 06:44:13</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>-33.236572,-71.459599</t>
+          <t>-33.107311,-71.551243</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>94.40000000000001</v>
+        <v>103.5</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>127527</v>
+        <v>194700.8</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>328.8</v>
+        <v>346.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>GV TM5 RXXG-15 E CABANILLA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 16:22:28</t>
+          <t>2026/09/15 06:44:17</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>-33.313616,-71.403502</t>
+          <t>-33.107653,-71.552374</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>101.7</v>
+        <v>99.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>26858.4</v>
+        <v>194700.9</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>256.8</v>
+        <v>346.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>GV TM5 RXXG-15 E CABANILLA</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 16:23:28</t>
+          <t>2026/09/17 06:46:31</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>-33.302435,-71.413644</t>
+          <t>-33.106461,-71.54952</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>93</v>
+        <v>107.5</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>26860</v>
+        <v>195035.5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>255.4</v>
+        <v>356</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 11:30:31</t>
+          <t>2026/09/17 06:46:49</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>-33.396277,-71.235683</t>
+          <t>-33.108365,-71.554765</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>107.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>68266.60000000001</v>
+        <v>195036.1</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>325.6</v>
+        <v>350.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 11:31:31</t>
+          <t>2026/09/17 06:56:52</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>-33.401837,-71.220196</t>
+          <t>-33.214018,-71.475197</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>100.1</v>
+        <v>105.3</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>68268.2</v>
+        <v>195051.8</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>271.7</v>
+        <v>344.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 11:32:33</t>
+          <t>2026/09/17 06:57:52</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>-33.405642,-71.203389</t>
+          <t>-33.226939,-71.467948</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Camino A Valparaíso, Curacaví, Melipilla, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>93.5</v>
+        <v>95.2</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>68269.8</v>
+        <v>195053.4</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>243.5</v>
+        <v>331.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
@@ -22597,33 +25079,33 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 16:22:30</t>
+          <t>2026/09/14 14:45:53</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>-33.289152,-71.411064</t>
+          <t>-33.055813,-71.494625</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>111.6</v>
+        <v>102.5</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>127129.3</v>
+        <v>58105.8</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>258.6</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
@@ -22631,67 +25113,67 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 16:23:29</t>
+          <t>2026/09/14 14:45:57</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>-33.30182,-71.410069</t>
+          <t>-33.05683,-71.494445</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>70.2</v>
+        <v>102.1</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>127130.7</v>
+        <v>58105.9</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>255.6</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 09:54:41</t>
+          <t>2026/09/14 14:46:10</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>-33.100871,-71.548054</t>
+          <t>-33.059683,-71.492753</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>100.7</v>
+        <v>98.8</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>127295.8</v>
+        <v>58106.3</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>335.9</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
@@ -22699,61 +25181,61 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 09:55:13</t>
+          <t>2026/09/17 08:37:57</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>-33.09365,-71.548732</t>
+          <t>-33.037226,-71.599772</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Avenida España, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>97.3</v>
+        <v>101.5</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>127296.6</v>
+        <v>58398.5</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>287.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 16:12:37</t>
+          <t>2026/09/17 08:38:57</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>-33.239795,-71.443276</t>
+          <t>-33.044476,-71.60931</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Avenida Errázuriz, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>102.9</v>
+        <v>68.3</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>127363.2</v>
+        <v>58399.8</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>268.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="52">
@@ -22763,37 +25245,37 @@
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2026/09/09 16:13:37</t>
+          <t>2026/09/14 10:02:32</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>-33.232671,-71.430065</t>
+          <t>-33.274413,-71.426352</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>89.2</v>
+        <v>100.6</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>127364.7</v>
+        <v>127875</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>282.4</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
@@ -22801,33 +25283,33 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 06:27:42</t>
+          <t>2026/09/14 10:03:13</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>-33.106618,-71.549921</t>
+          <t>-33.278598,-71.417789</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>100.4</v>
+        <v>70.5</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>274329.9</v>
+        <v>127876</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>350.3</v>
+        <v>327.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
@@ -22835,163 +25317,163 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 06:27:59</t>
+          <t>2026/09/14 17:36:13</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>-33.107925,-71.554121</t>
+          <t>-32.510195,-71.260059</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>67</v>
+        <v>100.7</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>274330.3</v>
+        <v>117968.6</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>348.3</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 10:46:59</t>
+          <t>2026/09/14 17:37:13</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>-33.013552,-71.500489</t>
+          <t>-32.525119,-71.26263</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>102.4</v>
+        <v>100.4</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>274762.9</v>
+        <v>117970.3</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>244.3</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 10:47:43</t>
+          <t>2026/09/14 17:38:14</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>-33.005348,-71.509123</t>
+          <t>-32.540188,-71.266199</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Avenida Carlos Ibáñez del Campo, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>99.8</v>
+        <v>100.7</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>274764.2</v>
+        <v>117972</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>209.9</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 11:02:44</t>
+          <t>2026/09/14 17:39:14</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>-32.944187,-71.513463</t>
+          <t>-32.554779,-71.266316</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>101.1</v>
+        <v>100.4</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>274777.9</v>
+        <v>117973.7</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>123</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 11:03:43</t>
+          <t>2026/09/14 17:40:13</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>-32.957448,-71.510369</t>
+          <t>-32.568326,-71.259134</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>86.90000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>274779.5</v>
+        <v>117975.4</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>173.7</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="59">
@@ -23005,27 +25487,27 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 15:48:56</t>
+          <t>2026/09/14 17:41:13</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>-32.487678,-71.16422</t>
+          <t>-32.581199,-71.250914</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>100.4</v>
+        <v>99.7</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>117789.7</v>
+        <v>117977</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>99.7</v>
+        <v>203.1</v>
       </c>
     </row>
     <row r="60">
@@ -23035,173 +25517,173 @@
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 15:49:55</t>
+          <t>2026/09/14 17:46:13</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>-32.487649,-71.149251</t>
+          <t>-32.644778,-71.229354</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>86.8</v>
+        <v>101.7</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>117791.1</v>
+        <v>117984.9</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>115</v>
+        <v>280.4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 06:41:35</t>
+          <t>2026/09/14 17:47:13</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>-32.597551,-71.361929</t>
+          <t>-32.657565,-71.220248</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>106.5</v>
+        <v>98.5</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>231818</v>
+        <v>117986.6</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>54.1</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 06:42:35</t>
+          <t>2026/09/14 17:50:13</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>-32.600693,-71.372316</t>
+          <t>-32.700376,-71.206916</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>6.7</v>
+        <v>100.1</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>231819</v>
+        <v>117991.5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>58</v>
+        <v>232.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 19:00:03</t>
+          <t>2026/09/14 17:51:13</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>-32.556391,-71.265273</t>
+          <t>-32.715205,-71.204808</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>107.3</v>
+        <v>100.3</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>231833.7</v>
+        <v>117993.2</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>110.7</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>2026/09/08 19:01:03</t>
+          <t>2026/09/14 17:52:14</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>-32.542699,-71.266639</t>
+          <t>-32.730254,-71.201462</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>92.40000000000001</v>
+        <v>100.3</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>231835.3</v>
+        <v>117994.9</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>113.5</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B65" s="12" t="n">
@@ -23209,401 +25691,3427 @@
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>2026/09/12 06:20:50</t>
+          <t>2026/09/14 17:53:13</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>-32.469627,-71.257078</t>
+          <t>-32.744564,-71.197611</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>103.1</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>232221</v>
+        <v>117996.5</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>50.7</v>
+        <v>214.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>2026/09/12 06:21:50</t>
+          <t>2026/09/15 06:06:59</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>-32.482903,-71.258026</t>
+          <t>-32.792331,-71.180419</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>77.59999999999999</v>
+        <v>101.2</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>232222.5</v>
+        <v>118039.5</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>55.9</v>
+        <v>234.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 06:30:01</t>
+          <t>2026/09/15 06:07:59</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>-32.458179,-71.347663</t>
+          <t>-32.787209,-71.167413</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Papudo, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>s/n, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>100.9</v>
+        <v>50.7</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>124291.2</v>
+        <v>118040.8</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>82.7</v>
+        <v>230.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2026/09/10 06:31:02</t>
+          <t>2026/09/15 06:08:59</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>-32.453391,-71.331811</t>
+          <t>-32.784921,-71.171999</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-30-F, Papudo, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>75.2</v>
+        <v>101.3</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>124292.7</v>
+        <v>118041.9</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>64</v>
+        <v>224.8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 18:03:38</t>
+          <t>2026/09/15 06:09:59</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>-33.024332,-71.500106</t>
+          <t>-32.774384,-71.184892</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Camino Internacional, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>124625.9</v>
+        <v>118043.6</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>196.7</v>
+        <v>213.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 18:04:02</t>
+          <t>2026/09/15 06:10:59</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>-33.029147,-71.499536</t>
+          <t>-32.762135,-71.194041</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Avenida Rubén Hurtado, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>70.40000000000001</v>
+        <v>100.7</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>124626.5</v>
+        <v>118045.2</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>185.9</v>
+        <v>209.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 19:21:04</t>
+          <t>2026/09/15 06:11:59</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>-33.064526,-71.481804</t>
+          <t>-32.74721,-71.196916</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>124657</v>
+        <v>118046.9</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>58.3</v>
+        <v>212.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>2026/09/11 19:21:37</t>
+          <t>2026/09/15 06:12:59</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>-33.060414,-71.489674</t>
+          <t>-32.732441,-71.200665</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>90.2</v>
+        <v>100.9</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>124657.9</v>
+        <v>118048.6</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>44.6</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 12:06:41</t>
+          <t>2026/09/15 06:13:59</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>-32.511341,-71.260012</t>
+          <t>-32.717647,-71.204302</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>285001.3</v>
+        <v>118050.3</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>81</v>
+        <v>224.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 12:07:41</t>
+          <t>2026/09/15 06:14:59</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>-32.49651,-71.258968</t>
+          <t>-32.70262,-71.206449</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>96.7</v>
+        <v>100.8</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>285003</v>
+        <v>118052</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>64</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>GV TOLVA SPGW-29 V OLIVARES</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026/09/07 16:26:43</t>
+          <t>2026/09/15 06:15:59</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>-33.179723,-71.506756</t>
+          <t>-32.687732,-71.209444</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>102.7</v>
+        <v>100.8</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>107204.2</v>
+        <v>118053.7</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>347.7</v>
+        <v>240.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>GV TOLVA SPGW-29 V OLIVARES</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B76" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:16:59</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>-32.67326,-71.212754</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>118055.3</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>244.3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:19:59</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>-32.633631,-71.231517</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>118060.2</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:21:00</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>-32.618623,-71.228808</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>118061.9</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>382.9</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:22:01</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>-32.618623,-71.228808</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>118062.2</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>382.9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:22:59</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>-32.591626,-71.243924</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>118065.2</v>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>274.4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:23:59</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>-32.579517,-71.25286</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>118066.8</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:26:59</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>-32.538069,-71.265541</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>118071.8</v>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>115.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:27:59</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>-32.523313,-71.262026</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>118073.5</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>106.3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:28:59</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>-32.508399,-71.259836</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>118075.1</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>80.90000000000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:29:59</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>-32.493383,-71.258738</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>118076.8</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 06:30:59</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>-32.479372,-71.257729</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>118078.3</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>54.3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:09:43</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>-32.570673,-71.258114</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>118291.5</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:10:43</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>-32.58345,-71.249727</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>118293.1</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>218.6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:11:35</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>-32.593706,-71.244038</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>118294.4</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>287.9</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:16:43</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>-32.657967,-71.219937</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>118302.4</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>256.2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:17:43</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>-32.671887,-71.213259</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>118304.1</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>247.9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:18:43</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>-32.686245,-71.209881</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>118305.7</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>240.2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:20:43</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>-32.715016,-71.20483</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>118308.9</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>226.8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:21:43</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>-32.729642,-71.201645</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>118310.6</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>221.8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:22:43</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>-32.744294,-71.197665</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>118312.3</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>215.8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:23:43</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>-32.75913,-71.194766</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>118314</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>210.8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:24:43</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>-32.772231,-71.187796</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>118315.6</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>215.3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:27:26</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>-32.792287,-71.184239</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>118319.6</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:27:43</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>-32.79032,-71.188361</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>118320.1</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>223.9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:28:43</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>-32.798265,-71.202449</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>118321.7</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>213.4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:29:43</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>-32.805203,-71.218053</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>118323.4</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>190.6</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:30:41</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>-32.818547,-71.223532</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>118325</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>194.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:30:43</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="inlineStr">
+        <is>
+          <t>-32.819045,-71.223428</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>118325.1</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>195.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:31:43</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>-32.833445,-71.220093</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>118326.8</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>165.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:32:43</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr">
+        <is>
+          <t>-32.842854,-71.223933</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>s/n, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>118327.8</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>153.9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 05:59:27</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>-32.857544,-71.224635</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>118346.3</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>147.7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:00:28</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="inlineStr">
+        <is>
+          <t>-32.842336,-71.223315</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>118348</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>161.1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:01:28</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>-32.828071,-71.222005</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>118349.7</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>170.9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:02:27</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>-32.813661,-71.223392</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>118351.4</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>185.8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:03:22</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>-32.802407,-71.214377</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>118352.9</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>194.8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:03:28</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
+        <is>
+          <t>-32.801726,-71.212789</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>118353.1</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:08:28</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>-32.775572,-71.183454</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>118360.4</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>215.6</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:09:28</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>-32.763862,-71.193721</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>118362.1</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>212.3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:10:27</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>-32.749228,-71.196422</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>118363.8</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>215.3</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:11:28</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr">
+        <is>
+          <t>-32.734219,-71.200035</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>118365.5</v>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>225.2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:12:28</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>-32.71954,-71.204017</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>118367.2</v>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>227.1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:13:28</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>-32.704554,-71.20613</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>118368.8</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>232.9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:14:27</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr">
+        <is>
+          <t>-32.689912,-71.208898</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>118370.5</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>237.8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:15:28</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>-32.674877,-71.212387</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>118372.2</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>245.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:16:28</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>-32.660707,-71.218272</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>118373.9</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>253.5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:17:28</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>-32.647615,-71.227099</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>118375.5</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>271.4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:18:22</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>-32.635433,-71.23198</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>118377</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>340.4</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:18:27</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>-32.634207,-71.231639</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>118377.2</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>345.4</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:19:28</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>-32.619226,-71.228578</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>118378.9</v>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>384.9</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:20:30</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>-32.619226,-71.228578</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>118379.2</v>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>384.9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:21:28</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>-32.592028,-71.243677</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>s/n, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>118382.2</v>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>279.6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:22:27</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="inlineStr">
+        <is>
+          <t>-32.579475,-71.252843</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>118383.9</v>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>189.1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:23:27</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>-32.565996,-71.260201</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>118385.6</v>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:24:28</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="inlineStr">
+        <is>
+          <t>-32.551997,-71.267618</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>118387.3</v>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>110.3</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:25:28</t>
+        </is>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>-32.537261,-71.265359</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>118389</v>
+      </c>
+      <c r="H130" s="12" t="n">
+        <v>117.7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:26:28</t>
+        </is>
+      </c>
+      <c r="D131" s="15" t="inlineStr">
+        <is>
+          <t>-32.522467,-71.261832</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>118390.6</v>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:27:27</t>
+        </is>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>-32.507749,-71.259758</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>118392.3</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>82.40000000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:28:28</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="inlineStr">
+        <is>
+          <t>-32.492431,-71.258674</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>118394</v>
+      </c>
+      <c r="H133" s="12" t="n">
+        <v>68.7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:29:28</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="inlineStr">
+        <is>
+          <t>-32.477371,-71.257589</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>118395.7</v>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>GP FOTON G7 TSVS-96</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:30:28</t>
+        </is>
+      </c>
+      <c r="D135" s="15" t="inlineStr">
+        <is>
+          <t>-32.46313,-71.256571</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>118397.3</v>
+      </c>
+      <c r="H135" s="12" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>GP DONGFENG DF6-RXDL-60</t>
+        </is>
+      </c>
+      <c r="B136" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/07 16:27:42</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>-33.191623,-71.49703</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>107205.8</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>364.1</v>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/14 06:55:01</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>-32.592889,-71.34664</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>232477.2</v>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>80.40000000000001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>GP DONGFENG DF6-RXDL-60</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/14 06:56:01</t>
+        </is>
+      </c>
+      <c r="D137" s="15" t="inlineStr">
+        <is>
+          <t>-32.597798,-71.362752</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>232478.8</v>
+      </c>
+      <c r="H137" s="12" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/14 05:07:37</t>
+        </is>
+      </c>
+      <c r="D138" s="15" t="inlineStr">
+        <is>
+          <t>-33.055616,-71.494675</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>124680.1</v>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/14 05:07:58</t>
+        </is>
+      </c>
+      <c r="D139" s="15" t="inlineStr">
+        <is>
+          <t>-33.06,-71.492156</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>124680.6</v>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B140" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 10:12:35</t>
+        </is>
+      </c>
+      <c r="D140" s="15" t="inlineStr">
+        <is>
+          <t>-32.467605,-71.185352</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-285, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>125272.2</v>
+      </c>
+      <c r="H140" s="12" t="n">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 10:13:11</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="inlineStr">
+        <is>
+          <t>-32.471502,-71.186986</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>125272.6</v>
+      </c>
+      <c r="H141" s="12" t="n">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B142" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 05:57:39</t>
+        </is>
+      </c>
+      <c r="D142" s="15" t="inlineStr">
+        <is>
+          <t>-32.486699,-71.146003</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>286839.9</v>
+      </c>
+      <c r="H142" s="12" t="n">
+        <v>112.4</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 05:58:39</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="inlineStr">
+        <is>
+          <t>-32.487748,-71.162813</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>286841.5</v>
+      </c>
+      <c r="H143" s="12" t="n">
+        <v>99.3</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B144" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:15:53</t>
+        </is>
+      </c>
+      <c r="D144" s="15" t="inlineStr">
+        <is>
+          <t>-32.539971,-71.265971</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>286898.4</v>
+      </c>
+      <c r="H144" s="12" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:16:54</t>
+        </is>
+      </c>
+      <c r="D145" s="15" t="inlineStr">
+        <is>
+          <t>-32.525162,-71.262459</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>286900.1</v>
+      </c>
+      <c r="H145" s="12" t="n">
+        <v>106.1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:17:53</t>
+        </is>
+      </c>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>-32.511285,-71.25998</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>286901.6</v>
+      </c>
+      <c r="H146" s="12" t="n">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/15 19:18:53</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>-32.496929,-71.258982</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>286903.2</v>
+      </c>
+      <c r="H147" s="12" t="n">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B148" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:30:42</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>-32.535383,-71.265062</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>286974.9</v>
+      </c>
+      <c r="H148" s="12" t="n">
+        <v>111.8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:31:42</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>-32.550003,-71.268371</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>286976.5</v>
+      </c>
+      <c r="H149" s="12" t="n">
+        <v>107.8</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B150" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:32:42</t>
+        </is>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>-32.562662,-71.262115</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F150" s="12" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>286978.1</v>
+      </c>
+      <c r="H150" s="12" t="n">
+        <v>119.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B151" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:38:42</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>-32.588954,-71.337067</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>286985.9</v>
+      </c>
+      <c r="H151" s="12" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B152" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/16 06:39:42</t>
+        </is>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>-32.594776,-71.351703</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>286987.4</v>
+      </c>
+      <c r="H152" s="12" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 06:30:25</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>-32.509066,-71.260013</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>287079.1</v>
+      </c>
+      <c r="H153" s="12" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B154" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 06:31:25</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>-32.52402,-71.262373</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>287080.7</v>
+      </c>
+      <c r="H154" s="12" t="n">
+        <v>103.9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 06:32:25</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>-32.538522,-71.265815</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>287082.4</v>
+      </c>
+      <c r="H155" s="12" t="n">
+        <v>113.5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B156" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:13:02</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="inlineStr">
+        <is>
+          <t>-32.58643,-71.330766</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F156" s="12" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>287102.9</v>
+      </c>
+      <c r="H156" s="12" t="n">
+        <v>83.40000000000001</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:13:55</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>-32.58039,-71.316058</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F157" s="12" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>287104.5</v>
+      </c>
+      <c r="H157" s="12" t="n">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:14:54</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="inlineStr">
+        <is>
+          <t>-32.575505,-71.301152</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>287106</v>
+      </c>
+      <c r="H158" s="12" t="n">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:20:54</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>-32.550098,-71.268187</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>287112.1</v>
+      </c>
+      <c r="H159" s="12" t="n">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B160" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:21:54</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>-32.535637,-71.264919</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>287113.7</v>
+      </c>
+      <c r="H160" s="12" t="n">
+        <v>117.1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:22:54</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>-32.520715,-71.261377</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>287115.4</v>
+      </c>
+      <c r="H161" s="12" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B162" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C162" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:23:54</t>
+        </is>
+      </c>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>-32.50592,-71.2596</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>287117.1</v>
+      </c>
+      <c r="H162" s="12" t="n">
+        <v>81.40000000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:24:54</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>-32.491347,-71.258547</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="F163" s="12" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>287118.7</v>
+      </c>
+      <c r="H163" s="12" t="n">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B164" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:51:54</t>
+        </is>
+      </c>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>-32.487695,-71.164224</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F164" s="12" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>287137.5</v>
+      </c>
+      <c r="H164" s="12" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>2026/09/17 19:52:54</t>
+        </is>
+      </c>
+      <c r="D165" s="15" t="inlineStr">
+        <is>
+          <t>-32.487289,-71.147938</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr">
+        <is>
+          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="F165" s="12" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>287139.1</v>
+      </c>
+      <c r="H165" s="12" t="n">
+        <v>114.7</v>
       </c>
     </row>
   </sheetData>
@@ -23684,12 +29192,101 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId160"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="default" paperSize="1" scale="100" pageOrder="downThenOver" blackAndWhite="0" draft="0" errors="displayed"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId72"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId161"/>
   </tableParts>
 </worksheet>
 </file>
--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O57" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:O57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O50" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:O50"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Conductor"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H165" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:H165"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H101" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:H101"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Secuencial" dataDxfId="0"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/09/26 23:59:59</t>
+          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/10/04 23:59:59</t>
         </is>
       </c>
     </row>
@@ -647,26 +647,26 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.008483796296296297</v>
+        <v>0.004456018518518519</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.001696759259259259</v>
+        <v>0.0005570023148148149</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>20.4</v>
+        <v>10.2</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>113.9</v>
+        <v>114</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>103.1</v>
+        <v>107.1</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -678,26 +678,26 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.003472222222222222</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>0.0006944444444444445</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>101.5</v>
+        <v>103.2</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
@@ -709,26 +709,26 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.002638888888888889</v>
+        <v>0.002881944444444444</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.0004398148148148148</v>
+        <v>0.0004803240740740741</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>107.5</v>
+        <v>103.6</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>103.6</v>
+        <v>101.8</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>0</v>
@@ -740,26 +740,26 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.0008912037037037037</v>
+        <v>0.004953703703703704</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.0004456018518518519</v>
+        <v>0.0003302430555555556</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>102.5</v>
+        <v>112.4</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>101.9</v>
+        <v>102.8</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -771,26 +771,26 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.000474537037037037</v>
+        <v>0.004351851851851852</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.000474537037037037</v>
+        <v>0.0006216898148148148</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>100.6</v>
+        <v>108.2</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>100.6</v>
+        <v>101.6</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
@@ -802,26 +802,26 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.03969907407407407</v>
+        <v>0.0007060185185185185</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.001890428240740741</v>
+        <v>0.0007060185185185185</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>94.40000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>101.7</v>
+        <v>100.3</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>100.6</v>
+        <v>100.3</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
@@ -833,26 +833,26 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.003668981481481481</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0009172453703703703</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>103.6</v>
+        <v>106.2</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>103.6</v>
+        <v>104</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
@@ -864,26 +864,26 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>0.0006597222222222222</v>
+        <v>0.001388888888888889</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>0.0003298611111111111</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>101</v>
+        <v>101.4</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>100.6</v>
+        <v>101.1</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>0</v>
@@ -895,26 +895,26 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GV TOLVA SPGW-29 V OLIVARES</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>0.01033564814814815</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.001148402777777778</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>24.2</v>
+        <v>1.1</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>106.9</v>
+        <v>101.4</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>102</v>
+        <v>101.4</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O392"/>
+  <dimension ref="A1:O427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -972,7 +972,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/14 00:00:00 Hasta: 2026/09/20 23:59:58</t>
+          <t>Desde : 2026/09/21 00:00:00 Hasta: 2026/09/27 23:59:58</t>
         </is>
       </c>
     </row>
@@ -20924,7 +20924,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
         <v>1</v>
       </c>
@@ -20983,7 +20982,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr"/>
       <c r="C349" t="n">
         <v>2</v>
       </c>
@@ -21042,7 +21040,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
         <v>1</v>
       </c>
@@ -21101,7 +21098,6 @@
           <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
         <v>1</v>
       </c>
@@ -21160,7 +21156,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
         <v>2</v>
       </c>
@@ -21219,7 +21214,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>3</v>
       </c>
@@ -21278,7 +21272,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>1</v>
       </c>
@@ -21337,7 +21330,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
         <v>3</v>
       </c>
@@ -21396,7 +21388,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
         <v>2</v>
       </c>
@@ -21455,7 +21446,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
         <v>3</v>
       </c>
@@ -21516,7 +21506,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
         <v>4</v>
       </c>
@@ -21575,7 +21564,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
         <v>5</v>
       </c>
@@ -21634,7 +21622,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
         <v>6</v>
       </c>
@@ -21693,7 +21680,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr"/>
       <c r="C361" t="n">
         <v>7</v>
       </c>
@@ -21752,7 +21738,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr"/>
       <c r="C362" t="n">
         <v>8</v>
       </c>
@@ -21811,7 +21796,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
         <v>9</v>
       </c>
@@ -21870,7 +21854,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
         <v>10</v>
       </c>
@@ -21929,7 +21912,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
         <v>11</v>
       </c>
@@ -21988,7 +21970,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr"/>
       <c r="C366" t="n">
         <v>12</v>
       </c>
@@ -22049,7 +22030,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr"/>
       <c r="C367" t="n">
         <v>1</v>
       </c>
@@ -22108,7 +22088,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
         <v>4</v>
       </c>
@@ -22167,7 +22146,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr"/>
       <c r="C369" t="n">
         <v>5</v>
       </c>
@@ -22226,7 +22204,6 @@
           <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr"/>
       <c r="C370" t="n">
         <v>4</v>
       </c>
@@ -22285,7 +22262,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr"/>
       <c r="C371" t="n">
         <v>13</v>
       </c>
@@ -22344,7 +22320,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr"/>
       <c r="C372" t="n">
         <v>14</v>
       </c>
@@ -22403,7 +22378,6 @@
           <t>GV TOLVA SPGW-29 V OLIVARES</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr"/>
       <c r="C373" t="n">
         <v>1</v>
       </c>
@@ -22462,7 +22436,6 @@
           <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr"/>
       <c r="C374" t="n">
         <v>1</v>
       </c>
@@ -22521,7 +22494,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr"/>
       <c r="C375" t="n">
         <v>6</v>
       </c>
@@ -22580,7 +22552,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
         <v>1</v>
       </c>
@@ -22639,7 +22610,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr"/>
       <c r="C377" t="n">
         <v>2</v>
       </c>
@@ -22698,7 +22668,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
         <v>3</v>
       </c>
@@ -22759,7 +22728,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr"/>
       <c r="C379" t="n">
         <v>4</v>
       </c>
@@ -22818,7 +22786,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr"/>
       <c r="C380" t="n">
         <v>5</v>
       </c>
@@ -22879,7 +22846,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr"/>
       <c r="C381" t="n">
         <v>6</v>
       </c>
@@ -22938,7 +22904,6 @@
           <t>GP FOTON G7 TSVS-96</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr"/>
       <c r="C382" t="n">
         <v>7</v>
       </c>
@@ -22997,7 +22962,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
         <v>1</v>
       </c>
@@ -23056,7 +23020,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr"/>
       <c r="C384" t="n">
         <v>2</v>
       </c>
@@ -23115,7 +23078,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr"/>
       <c r="C385" t="n">
         <v>3</v>
       </c>
@@ -23174,7 +23136,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr"/>
       <c r="C386" t="n">
         <v>4</v>
       </c>
@@ -23233,7 +23194,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr"/>
       <c r="C387" t="n">
         <v>5</v>
       </c>
@@ -23292,7 +23252,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr"/>
       <c r="C388" t="n">
         <v>6</v>
       </c>
@@ -23351,7 +23310,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr"/>
       <c r="C389" t="n">
         <v>7</v>
       </c>
@@ -23410,7 +23368,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr"/>
       <c r="C390" t="n">
         <v>8</v>
       </c>
@@ -23469,7 +23426,6 @@
           <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr"/>
       <c r="C391" t="n">
         <v>2</v>
       </c>
@@ -23528,7 +23484,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr"/>
       <c r="C392" t="n">
         <v>15</v>
       </c>
@@ -23578,6 +23533,2073 @@
         <v>0</v>
       </c>
       <c r="O392" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="n">
+        <v>1</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026/09/28 06:32:57</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-32.574246,-71.296456</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2026/09/28 06:33:57</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-32.577993,-71.310394</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J393" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K393" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L393" t="n">
+        <v>103</v>
+      </c>
+      <c r="M393" t="n">
+        <v>103</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0</v>
+      </c>
+      <c r="O393" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="n">
+        <v>1</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026/09/28 10:15:29</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-33.168001,-71.528768</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026/09/28 10:16:29</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-33.160178,-71.543995</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J394" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K394" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L394" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="M394" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="N394" t="n">
+        <v>0</v>
+      </c>
+      <c r="O394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="n">
+        <v>1</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026/09/28 13:42:04</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-33.101625,-71.548022</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026/09/28 13:42:27</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-33.096487,-71.545769</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J395" s="14" t="n">
+        <v>0.0002662037037037037</v>
+      </c>
+      <c r="K395" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L395" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="M395" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="N395" t="n">
+        <v>0</v>
+      </c>
+      <c r="O395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="n">
+        <v>2</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026/09/28 19:04:41</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-32.560324,-71.263216</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026/09/28 19:05:41</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-32.546247,-71.267475</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J396" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K396" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L396" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="M396" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="N396" t="n">
+        <v>0</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="n">
+        <v>1</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026/09/29 11:40:22</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-33.603372,-71.47727</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>2026/09/29 11:41:22</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-33.593699,-71.490824</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Ruta 78, San Antonio, San Antonio, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J397" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K397" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L397" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="M397" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="N397" t="n">
+        <v>0</v>
+      </c>
+      <c r="O397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="n">
+        <v>2</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026/09/29 11:42:22</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-33.581291,-71.502394</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Ruta 78, San Antonio, San Antonio, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026/09/29 11:43:22</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-33.570975,-71.518278</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Ruta 78, Cartagena, San Antonio, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J398" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K398" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L398" t="n">
+        <v>114</v>
+      </c>
+      <c r="M398" t="n">
+        <v>114</v>
+      </c>
+      <c r="N398" t="n">
+        <v>0</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="n">
+        <v>2</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026/09/29 17:17:40</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-33.093247,-71.549279</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026/09/29 17:18:40</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-33.08311,-71.560254</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J399" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K399" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L399" t="n">
+        <v>101</v>
+      </c>
+      <c r="M399" t="n">
+        <v>101</v>
+      </c>
+      <c r="N399" t="n">
+        <v>0</v>
+      </c>
+      <c r="O399" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>GC TSVS-89 M AEDO</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="n">
+        <v>3</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026/09/29 19:10:45</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-32.551068,-71.268055</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2026/09/29 19:11:45</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-32.536671,-71.265216</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J400" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K400" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L400" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M400" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="N400" t="n">
+        <v>0</v>
+      </c>
+      <c r="O400" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="n">
+        <v>3</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026/09/30 07:10:20</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-33.165496,-71.533858</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026/09/30 07:11:20</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-33.173279,-71.518683</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J401" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K401" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L401" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="M401" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0</v>
+      </c>
+      <c r="O401" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026/09/30 11:46:33</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-33.089695,-71.541744</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026/09/30 11:46:54</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>-33.094334,-71.54287</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J402" s="14" t="n">
+        <v>0.0002430555555555555</v>
+      </c>
+      <c r="K402" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L402" t="n">
+        <v>101</v>
+      </c>
+      <c r="M402" t="n">
+        <v>101</v>
+      </c>
+      <c r="N402" t="n">
+        <v>0</v>
+      </c>
+      <c r="O402" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="n">
+        <v>1</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026/09/30 12:19:08</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-33.094687,-71.543221</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026/09/30 12:19:25</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-33.097142,-71.547094</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J403" s="14" t="n">
+        <v>0.0001967592592592593</v>
+      </c>
+      <c r="K403" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L403" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="M403" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="N403" t="n">
+        <v>0</v>
+      </c>
+      <c r="O403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="n">
+        <v>2</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026/09/30 12:26:39</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-33.080948,-71.625491</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026/09/30 12:26:52</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-33.07768,-71.626619</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J404" s="14" t="n">
+        <v>0.000150462962962963</v>
+      </c>
+      <c r="K404" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L404" t="n">
+        <v>107</v>
+      </c>
+      <c r="M404" t="n">
+        <v>107</v>
+      </c>
+      <c r="N404" t="n">
+        <v>0</v>
+      </c>
+      <c r="O404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="n">
+        <v>2</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026/09/30 13:48:33</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-33.066452,-71.635573</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2026/09/30 13:49:07</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-33.071629,-71.628251</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J405" s="14" t="n">
+        <v>0.0003935185185185185</v>
+      </c>
+      <c r="K405" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L405" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="M405" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="n">
+        <v>3</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026/09/30 13:56:07</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-33.112723,-71.560127</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2026/09/30 13:56:49</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-33.121192,-71.561406</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J406" s="14" t="n">
+        <v>0.0004861111111111111</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L406" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M406" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N406" t="n">
+        <v>0</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="n">
+        <v>4</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026/09/30 16:26:24</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-33.235353,-71.460898</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2026/09/30 16:27:24</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-33.223146,-71.469762</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J407" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K407" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L407" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="M407" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>DONGFENG DF6 SRSR-97</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="n">
+        <v>1</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026/10/01 05:23:14</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-33.202935,-71.486925</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026/10/01 05:24:14</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-33.191336,-71.497001</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J408" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K408" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L408" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M408" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N408" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="n">
+        <v>5</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026/10/01 06:52:59</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-33.105892,-71.548968</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2026/10/01 06:53:41</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-33.111009,-71.559679</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J409" s="14" t="n">
+        <v>0.0004861111111111111</v>
+      </c>
+      <c r="K409" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L409" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="M409" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="N409" t="n">
+        <v>0</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="n">
+        <v>6</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026/10/01 07:02:14</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-33.20296,-71.487041</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2026/10/01 07:03:14</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-33.213784,-71.475388</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J410" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K410" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L410" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="M410" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="n">
+        <v>4</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026/10/01 08:52:29</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-33.094963,-71.543668</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026/10/01 08:52:48</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-33.097684,-71.548109</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J411" s="14" t="n">
+        <v>0.0002199074074074074</v>
+      </c>
+      <c r="K411" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L411" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="M411" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>5</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026/10/01 10:30:48</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-33.083354,-71.619375</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2026/10/01 10:31:18</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-33.089041,-71.615554</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J412" s="14" t="n">
+        <v>0.0003472222222222222</v>
+      </c>
+      <c r="K412" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L412" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="M412" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="N412" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>6</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026/10/01 10:38:38</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-33.086219,-71.543703</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2026/10/01 10:39:18</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-33.078192,-71.546987</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J413" s="14" t="n">
+        <v>0.000462962962962963</v>
+      </c>
+      <c r="K413" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L413" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="M413" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="N413" t="n">
+        <v>0</v>
+      </c>
+      <c r="O413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>7</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026/10/01 16:21:31</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-33.093788,-71.548631</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2026/10/01 16:22:14</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-33.087505,-71.558595</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J414" s="14" t="n">
+        <v>0.0004976851851851852</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L414" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="M414" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>DONGFENG DF6 SRSR-97</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>2</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026/10/02 08:35:07</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-32.951726,-71.509423</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2026/10/02 08:35:46</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-32.943273,-71.513582</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J415" s="14" t="n">
+        <v>0.0004513888888888889</v>
+      </c>
+      <c r="K415" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L415" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M415" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N415" t="n">
+        <v>0</v>
+      </c>
+      <c r="O415" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="n">
+        <v>1</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026/10/02 08:36:19</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-33.172529,-71.520037</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2026/10/02 08:37:19</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-33.180557,-71.50586</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J416" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K416" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L416" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="M416" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="N416" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="n">
+        <v>7</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026/10/02 09:08:34</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-32.951403,-71.509712</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2026/10/02 09:08:47</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-32.954427,-71.509305</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J417" s="14" t="n">
+        <v>0.000150462962962963</v>
+      </c>
+      <c r="K417" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L417" t="n">
+        <v>101</v>
+      </c>
+      <c r="M417" t="n">
+        <v>101</v>
+      </c>
+      <c r="N417" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="n">
+        <v>1</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026/10/02 09:46:19</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-32.839171,-71.113368</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2026/10/02 09:47:14</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-32.846,-71.100759</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J418" s="14" t="n">
+        <v>0.0006365740740740741</v>
+      </c>
+      <c r="K418" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L418" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M418" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N418" t="n">
+        <v>0</v>
+      </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="n">
+        <v>2</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:01:19</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-32.853244,-70.911949</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:02:19</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-32.852206,-70.894789</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J419" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K419" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L419" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="M419" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="N419" t="n">
+        <v>0</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="n">
+        <v>3</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:03:19</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-32.851113,-70.877393</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:04:19</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-32.853791,-70.86286</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="J420" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K420" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L420" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M420" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N420" t="n">
+        <v>0</v>
+      </c>
+      <c r="O420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="n">
+        <v>4</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:10:19</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-32.915851,-70.811644</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:11:19</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-32.930469,-70.812007</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Panamericana Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J421" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K421" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L421" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M421" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="n">
+        <v>5</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:17:19</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-32.996391,-70.872991</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Panamericana Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:18:19</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-33.005228,-70.885492</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J422" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K422" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L422" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M422" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N422" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="n">
+        <v>6</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:29:19</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-33.129061,-70.816603</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>2026/10/02 10:30:19</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-33.140738,-70.806368</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J423" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K423" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L423" t="n">
+        <v>104</v>
+      </c>
+      <c r="M423" t="n">
+        <v>104</v>
+      </c>
+      <c r="N423" t="n">
+        <v>0</v>
+      </c>
+      <c r="O423" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>GC TM5-RXXG-13 D SILVA</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="n">
+        <v>1</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026/10/02 17:14:31</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-32.841413,-71.075304</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2026/10/02 17:15:32</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-32.838415,-71.058687</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J424" s="14" t="n">
+        <v>0.0007060185185185185</v>
+      </c>
+      <c r="K424" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L424" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M424" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N424" t="n">
+        <v>0</v>
+      </c>
+      <c r="O424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="n">
+        <v>2</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026/10/03 08:18:48</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-33.107431,-71.551712</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2026/10/03 08:19:21</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-33.110977,-71.559643</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J425" s="14" t="n">
+        <v>0.0003819444444444445</v>
+      </c>
+      <c r="K425" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L425" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M425" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="N425" t="n">
+        <v>0</v>
+      </c>
+      <c r="O425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="n">
+        <v>8</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026/10/03 15:58:08</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-33.083555,-71.6193</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2026/10/03 15:58:18</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-33.08584,-71.618512</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J426" s="14" t="n">
+        <v>0.0001157407407407407</v>
+      </c>
+      <c r="K426" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L426" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="M426" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="N426" t="n">
+        <v>0</v>
+      </c>
+      <c r="O426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="n">
+        <v>9</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026/10/04 23:59:57</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-33.0902,-71.611533</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2026/10/04 23:59:57</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-33.0902,-71.611533</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J427" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L427" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M427" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N427" t="n">
+        <v>0</v>
+      </c>
+      <c r="O427" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23602,7 +25624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -23628,7 +25650,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/14 00:00:00 Hasta: 2026/09/20 23:59:58</t>
+          <t>Desde : 2026/09/21 00:00:00 Hasta: 2026/09/27 23:59:58</t>
         </is>
       </c>
     </row>
@@ -23677,7 +25699,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -23685,33 +25707,33 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 11:35:40</t>
+          <t>2026/09/21 16:30:44</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-33.096592,-71.546281</t>
+          <t>-33.064531,-71.582122</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>100.3</v>
+        <v>100.8</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>63880.5</v>
+        <v>195385.6</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>314.1</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
@@ -23719,67 +25741,67 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 11:35:54</t>
+          <t>2026/09/21 16:31:03</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>-33.098578,-71.548812</t>
+          <t>-33.068343,-71.57905</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>77.40000000000001</v>
+        <v>102.2</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>63880.9</v>
+        <v>195386.2</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>328.4</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:01:00</t>
+          <t>2026/09/21 16:31:43</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-33.167229,-71.530493</t>
+          <t>-33.073399,-71.569769</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>111.4</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>64193.3</v>
+        <v>195387.2</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>344.8</v>
+        <v>164.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
@@ -23787,33 +25809,33 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:02:00</t>
+          <t>2026/09/22 06:52:22</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>-33.1753,-71.514666</t>
+          <t>-33.106964,-71.550335</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>101.7</v>
+        <v>103.2</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>64195</v>
+        <v>195486.9</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>349.9</v>
+        <v>349.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -23821,46 +25843,46 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:03:00</t>
+          <t>2026/09/22 06:52:42</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-33.186116,-71.501403</t>
+          <t>-33.108835,-71.556265</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>105</v>
+        <v>97.3</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>64196.8</v>
+        <v>195487.5</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>351.6</v>
+        <v>347.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:04:00</t>
+          <t>2026/09/22 06:58:45</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-33.199588,-71.490643</t>
+          <t>-33.174097,-71.517021</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -23869,134 +25891,134 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>106.8</v>
+        <v>103</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>64198.6</v>
+        <v>195497.1</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>376.6</v>
+        <v>350.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:05:00</t>
+          <t>2026/09/22 06:59:45</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-33.210571,-71.478795</t>
+          <t>-33.182965,-71.503923</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>113.9</v>
+        <v>94.2</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>64200.2</v>
+        <v>195498.7</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>357.6</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:06:00</t>
+          <t>2026/09/23 06:47:44</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>-33.225062,-71.468933</t>
+          <t>-33.106438,-71.549498</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>64202.1</v>
+        <v>195843.1</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>325.9</v>
+        <v>358.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:07:00</t>
+          <t>2026/09/23 06:48:23</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-33.237036,-71.459138</t>
+          <t>-33.110597,-71.559406</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>106.2</v>
+        <v>95.3</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>64203.7</v>
+        <v>195844.2</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>317.8</v>
+        <v>343.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:08:00</t>
+          <t>2026/09/23 07:01:26</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-33.249098,-71.445932</t>
+          <t>-33.254285,-71.441848</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -24005,32 +26027,32 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>105.8</v>
+        <v>113</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>64205.5</v>
+        <v>195864.9</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>261.5</v>
+        <v>262.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:08:59</t>
+          <t>2026/09/23 07:01:53</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-33.259158,-71.438359</t>
+          <t>-33.259087,-71.438325</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -24039,168 +26061,168 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>24.2</v>
+        <v>34.9</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>64206.8</v>
+        <v>195865.5</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>275.1</v>
+        <v>275.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:42:37</t>
+          <t>2026/09/24 06:55:05</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>-33.221243,-71.470765</t>
+          <t>-33.170963,-71.523157</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>101.9</v>
+        <v>107.3</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>64214.9</v>
+        <v>196096.4</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>333.5</v>
+        <v>347.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:43:37</t>
+          <t>2026/09/24 06:56:05</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-33.209398,-71.479899</t>
+          <t>-33.178557,-71.508373</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>90.5</v>
+        <v>92.8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>64216.4</v>
+        <v>196098</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>372.9</v>
+        <v>350.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:44:37</t>
+          <t>2026/09/24 16:07:24</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>-33.198486,-71.49131</t>
+          <t>-33.259735,-71.437511</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>100.2</v>
+        <v>107.1</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>64218.1</v>
+        <v>196267.7</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>372.1</v>
+        <v>284.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:45:37</t>
+          <t>2026/09/24 16:08:24</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-33.18722,-71.500328</t>
+          <t>-33.247305,-71.447136</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>82.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>64219.6</v>
+        <v>196269.3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>355.4</v>
+        <v>267.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 16:01:37</t>
+          <t>2026/09/24 16:17:24</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>-33.141488,-71.562336</t>
+          <t>-33.158164,-71.548034</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -24209,32 +26231,32 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>101.8</v>
+        <v>107.9</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>64227.4</v>
+        <v>196283.3</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>336.4</v>
+        <v>359.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 16:02:37</t>
+          <t>2026/09/24 16:18:24</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-33.126063,-71.561539</t>
+          <t>-33.148261,-71.559017</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -24243,53 +26265,53 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>109.1</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>64229.1</v>
+        <v>196284.8</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>339.3</v>
+        <v>338.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>GLP SSZD-71  J VALLEJOS</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 16:03:37</t>
+          <t>2026/09/23 17:41:07</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>-33.110375,-71.55904</t>
+          <t>-32.986627,-71.500563</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>91.7</v>
+        <v>103.2</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>64230.9</v>
+        <v>29442.9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>344.2</v>
+        <v>132.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
@@ -24297,33 +26319,33 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 14:27:50</t>
+          <t>2026/09/23 17:42:07</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-33.220359,-71.391567</t>
+          <t>-32.972873,-71.499375</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>101.9</v>
+        <v>79</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>84090.10000000001</v>
+        <v>29444.4</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>308.4</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
@@ -24331,67 +26353,67 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 14:28:50</t>
+          <t>2026/09/24 10:17:48</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>-33.207985,-71.385576</t>
+          <t>-33.103997,-71.548121</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>92.3</v>
+        <v>103.2</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>84091.60000000001</v>
+        <v>129532.5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>317.2</v>
+        <v>355.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 07:25:22</t>
+          <t>2026/09/24 10:18:21</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-33.157629,-71.548991</t>
+          <t>-33.096468,-71.545796</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>100.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>84169</v>
+        <v>129533.3</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>370.4</v>
+        <v>311.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
@@ -24399,67 +26421,67 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 07:26:22</t>
+          <t>2026/09/24 11:04:51</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>-33.147258,-71.559468</t>
+          <t>-32.74668,-71.418272</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>97.3</v>
+        <v>100.5</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>84170.5</v>
+        <v>129586.5</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>341.6</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 08:23:38</t>
+          <t>2026/09/24 11:05:39</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-32.886351,-71.453382</t>
+          <t>-32.736764,-71.417754</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>100.9</v>
+        <v>21.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>84216.8</v>
+        <v>129587.5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>140.5</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
@@ -24467,67 +26489,67 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 08:24:38</t>
+          <t>2026/09/24 14:27:11</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>-32.875885,-71.455694</t>
+          <t>-32.697632,-71.434125</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>52.5</v>
+        <v>100.8</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>84218</v>
+        <v>129611.9</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>120</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:20:42</t>
+          <t>2026/09/24 14:28:11</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>-33.169856,-71.525302</t>
+          <t>-32.711743,-71.439001</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>103.4</v>
+        <v>97</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>84466.10000000001</v>
+        <v>129613.6</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>347.2</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
@@ -24535,67 +26557,67 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:21:42</t>
+          <t>2026/09/24 14:30:11</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>-33.176949,-71.511477</t>
+          <t>-32.736397,-71.430255</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>84.09999999999999</v>
+        <v>101.4</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>84467.60000000001</v>
+        <v>129616.9</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>347.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:26:42</t>
+          <t>2026/09/24 14:31:07</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-33.234051,-71.462338</t>
+          <t>-32.73887,-71.417684</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>100.8</v>
+        <v>19</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>84475.5</v>
+        <v>129618.1</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>337.6</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GV TDLD-98 J PACHECHO</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
@@ -24603,46 +26625,46 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026/09/16 15:27:42</t>
+          <t>2026/09/24 15:17:42</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>-33.244005,-71.449885</t>
+          <t>-33.106519,-71.549636</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>s/n, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>90.40000000000001</v>
+        <v>101.3</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>84477.10000000001</v>
+        <v>129673.6</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>267.9</v>
+        <v>354.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 13:37:23</t>
+          <t>2026/09/24 15:18:16</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-33.102549,-71.548051</t>
+          <t>-33.109626,-71.558333</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -24651,257 +26673,257 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>100.6</v>
+        <v>89</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>194468.2</v>
+        <v>129674.5</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>344.1</v>
+        <v>354.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 13:37:48</t>
+          <t>2026/09/24 16:03:25</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>-33.09657,-71.545933</t>
+          <t>-33.225873,-71.408757</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>96.7</v>
+        <v>103.6</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>194468.8</v>
+        <v>129705.7</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>312</v>
+        <v>298.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 13:38:22</t>
+          <t>2026/09/24 16:03:43</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>-33.089883,-71.541658</t>
+          <t>-33.226252,-71.403608</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>100.2</v>
+        <v>97.5</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>194469.7</v>
+        <v>129706.2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>321.1</v>
+        <v>297.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 13:38:23</t>
+          <t>2026/09/22 07:45:10</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>-33.089633,-71.54168</t>
+          <t>-33.100187,-71.547878</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>100.1</v>
+        <v>105.1</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>194469.8</v>
+        <v>278693.6</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>322.3</v>
+        <v>329.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 13:39:23</t>
+          <t>2026/09/22 07:45:36</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>-33.078859,-71.546943</t>
+          <t>-33.095247,-71.543902</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>44.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>194471.1</v>
+        <v>278694.3</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>312</v>
+        <v>312.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 16:20:08</t>
+          <t>2026/09/22 20:35:30</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>-33.124523,-71.56142</t>
+          <t>-33.07978,-71.626201</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>104.3</v>
+        <v>100.6</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>194616.5</v>
+        <v>278813.7</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>339.9</v>
+        <v>459.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 16:21:08</t>
+          <t>2026/09/22 20:36:02</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>-33.139039,-71.562985</t>
+          <t>-33.074449,-71.627144</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>95.59999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>194618.1</v>
+        <v>278814.3</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>332.5</v>
+        <v>431.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:44:13</t>
+          <t>2026/09/22 21:09:48</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>-33.107311,-71.551243</t>
+          <t>-33.07467,-71.627206</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>103.5</v>
+        <v>102.1</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>194700.8</v>
+        <v>278823.6</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>346.7</v>
+        <v>443.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B42" s="12" t="n">
@@ -24909,67 +26931,67 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:44:17</t>
+          <t>2026/09/22 21:10:22</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>-33.107653,-71.552374</t>
+          <t>-33.081773,-71.624192</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>99.8</v>
+        <v>102.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>194700.9</v>
+        <v>278824.5</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>346.4</v>
+        <v>476.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026/09/17 06:46:31</t>
+          <t>2026/09/22 21:10:41</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>-33.106461,-71.54952</t>
+          <t>-33.083436,-71.619366</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>107.5</v>
+        <v>74.5</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>195035.5</v>
+        <v>278825</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>356</v>
+        <v>478.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
@@ -24977,843 +26999,843 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>2026/09/17 06:46:49</t>
+          <t>2026/09/22 21:12:11</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>-33.108365,-71.554765</t>
+          <t>-33.093374,-71.603202</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>92.59999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>195036.1</v>
+        <v>278827.1</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>350.2</v>
+        <v>422.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026/09/17 06:56:52</t>
+          <t>2026/09/22 21:12:28</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>-33.214018,-71.475197</t>
+          <t>-33.095154,-71.599305</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>105.3</v>
+        <v>102.2</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>195051.8</v>
+        <v>278827.5</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>344.9</v>
+        <v>439.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>2026/09/17 06:57:52</t>
+          <t>2026/09/22 21:12:49</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>-33.226939,-71.467948</t>
+          <t>-33.094276,-71.592863</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>95.2</v>
+        <v>107</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>195053.4</v>
+        <v>278828.2</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>331.5</v>
+        <v>452.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 14:45:53</t>
+          <t>2026/09/22 21:13:50</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>-33.055813,-71.494625</t>
+          <t>-33.098312,-71.576965</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>102.5</v>
+        <v>87.3</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>58105.8</v>
+        <v>278829.8</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>23.1</v>
+        <v>433.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 14:45:57</t>
+          <t>2026/09/22 21:15:50</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>-33.05683,-71.494445</t>
+          <t>-33.108176,-71.555779</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>102.1</v>
+        <v>101.2</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>58105.9</v>
+        <v>278832.7</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>23.3</v>
+        <v>343.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 14:46:10</t>
+          <t>2026/09/22 21:16:02</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>-33.059683,-71.492753</t>
+          <t>-33.109708,-71.554261</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>98.8</v>
+        <v>33</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>58106.3</v>
+        <v>278832.9</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>32.2</v>
+        <v>346.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>2026/09/17 08:37:57</t>
+          <t>2026/09/22 21:16:51</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>-33.037226,-71.599772</t>
+          <t>-33.102198,-71.548</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Avenida España, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>101.5</v>
+        <v>107.1</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>58398.5</v>
+        <v>278834.1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>3.4</v>
+        <v>347.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSK-54 TOPOGRAFIA</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026/09/17 08:38:57</t>
+          <t>2026/09/22 21:17:15</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>-33.044476,-71.60931</t>
+          <t>-33.096372,-71.545629</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Avenida Errázuriz, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>68.3</v>
+        <v>100.9</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>58399.8</v>
+        <v>278834.7</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>3.6</v>
+        <v>318.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 10:02:32</t>
+          <t>2026/09/22 21:17:45</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>-33.274413,-71.426352</t>
+          <t>-33.090113,-71.541609</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>100.6</v>
+        <v>102.1</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>127875</v>
+        <v>278835.6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>291</v>
+        <v>329.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 10:03:13</t>
+          <t>2026/09/22 21:17:51</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>-33.278598,-71.417789</t>
+          <t>-33.088636,-71.541976</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-852, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>70.5</v>
+        <v>101</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>127876</v>
+        <v>278835.8</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>327.3</v>
+        <v>334.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:36:13</t>
+          <t>2026/09/22 21:18:40</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>-32.510195,-71.260059</t>
+          <t>-33.07789,-71.54688</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>100.7</v>
+        <v>66.8</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>117968.6</v>
+        <v>278837.1</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>77.59999999999999</v>
+        <v>322.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:37:13</t>
+          <t>2026/09/22 21:20:51</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>-32.525119,-71.26263</t>
+          <t>-33.056024,-71.529652</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>100.4</v>
+        <v>102</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>117970.3</v>
+        <v>278840.4</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>101.7</v>
+        <v>267.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:38:14</t>
+          <t>2026/09/22 21:21:04</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>-32.540188,-71.266199</t>
+          <t>-33.052977,-71.529235</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>100.7</v>
+        <v>97.5</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>117972</v>
+        <v>278840.7</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>107.1</v>
+        <v>249.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:39:14</t>
+          <t>2026/09/22 21:21:51</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>-32.554779,-71.266316</t>
+          <t>-33.050259,-71.526545</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>100.4</v>
+        <v>103.3</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>117973.7</v>
+        <v>278841.9</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>108.5</v>
+        <v>192.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:40:13</t>
+          <t>2026/09/22 21:22:04</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>-32.568326,-71.259134</t>
+          <t>-33.052978,-71.525812</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>100.1</v>
+        <v>77.7</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>117975.4</v>
+        <v>278842.2</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>129.8</v>
+        <v>171.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:41:13</t>
+          <t>2026/09/22 22:52:53</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>-32.581199,-71.250914</t>
+          <t>-33.080648,-71.5467</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>99.7</v>
+        <v>100.7</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>117977</v>
+        <v>278856.2</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>203.1</v>
+        <v>301.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:46:13</t>
+          <t>2026/09/22 22:53:54</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>-32.644778,-71.229354</t>
+          <t>-33.094237,-71.542709</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>101.7</v>
+        <v>94.2</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>117984.9</v>
+        <v>278857.8</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>280.4</v>
+        <v>317.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:47:13</t>
+          <t>2026/09/22 23:00:53</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>-32.657565,-71.220248</t>
+          <t>-33.080785,-71.625629</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>98.5</v>
+        <v>100.6</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>117986.6</v>
+        <v>278868.4</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>256</v>
+        <v>463.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:50:13</t>
+          <t>2026/09/22 23:00:55</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>-32.700376,-71.206916</t>
+          <t>-33.080376,-71.625952</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>100.1</v>
+        <v>97.7</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>117991.5</v>
+        <v>278868.4</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>232.7</v>
+        <v>463.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:51:13</t>
+          <t>2026/09/23 16:22:13</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>-32.715205,-71.204808</t>
+          <t>-33.067759,-71.633023</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>100.3</v>
+        <v>112.4</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>117993.2</v>
+        <v>279237.2</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>225</v>
+        <v>435</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:52:14</t>
+          <t>2026/09/23 16:22:39</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>-32.730254,-71.201462</t>
+          <t>-33.072648,-71.627581</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>100.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>117994.9</v>
+        <v>279237.9</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>219.5</v>
+        <v>431.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>2026/09/14 17:53:13</t>
+          <t>2026/09/23 16:59:32</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>-32.744564,-71.197611</t>
+          <t>-33.067309,-71.53576</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>99.59999999999999</v>
+        <v>100.7</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>117996.5</v>
+        <v>279259.6</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>214.5</v>
+        <v>317</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:06:59</t>
+          <t>2026/09/23 16:59:57</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>-32.792331,-71.180419</t>
+          <t>-33.06375,-71.530232</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>101.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>118039.5</v>
+        <v>279260.3</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>234.3</v>
+        <v>287.9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:07:59</t>
+          <t>2026/09/26 05:57:45</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>-32.787209,-71.167413</t>
+          <t>-33.090501,-71.541783</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>s/n, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>50.7</v>
+        <v>101.5</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>118040.8</v>
+        <v>280508</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>230.3</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:08:59</t>
+          <t>2026/09/26 05:58:06</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>-32.784921,-71.171999</t>
+          <t>-33.094862,-71.543568</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>101.3</v>
+        <v>91.7</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>118041.9</v>
+        <v>280508.6</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>224.8</v>
+        <v>315.8</v>
       </c>
     </row>
     <row r="69">
@@ -25823,31 +27845,31 @@
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:09:59</t>
+          <t>2026/09/24 08:59:37</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>-32.774384,-71.184892</t>
+          <t>-32.739544,-71.198615</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>100.7</v>
+        <v>100.1</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>118043.6</v>
+        <v>119341.6</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>213.7</v>
+        <v>227.8</v>
       </c>
     </row>
     <row r="70">
@@ -25857,16 +27879,16 @@
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:10:59</t>
+          <t>2026/09/24 09:00:37</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>-32.762135,-71.194041</t>
+          <t>-32.752198,-71.196065</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -25875,13 +27897,13 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>100.7</v>
+        <v>87</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>118045.2</v>
+        <v>119343.1</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>209.7</v>
+        <v>216.1</v>
       </c>
     </row>
     <row r="71">
@@ -25891,31 +27913,31 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:11:59</t>
+          <t>2026/09/24 09:09:37</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>-32.74721,-71.196916</t>
+          <t>-32.83366,-71.220176</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>100.9</v>
+        <v>100.4</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>118046.9</v>
+        <v>119356.7</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>212.9</v>
+        <v>166.3</v>
       </c>
     </row>
     <row r="72">
@@ -25925,31 +27947,31 @@
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:12:59</t>
+          <t>2026/09/24 09:10:37</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>-32.732441,-71.200665</t>
+          <t>-32.848271,-71.224416</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>100.9</v>
+        <v>100.6</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>118048.6</v>
+        <v>119358.4</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>221</v>
+        <v>150.1</v>
       </c>
     </row>
     <row r="73">
@@ -25959,31 +27981,31 @@
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:13:59</t>
+          <t>2026/09/24 09:11:37</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>-32.717647,-71.204302</t>
+          <t>-32.863138,-71.226828</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>100.7</v>
+        <v>100.3</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>118050.3</v>
+        <v>119360.1</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>224.8</v>
+        <v>138.9</v>
       </c>
     </row>
     <row r="74">
@@ -25993,31 +28015,31 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:14:59</t>
+          <t>2026/09/24 09:12:37</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>-32.70262,-71.206449</t>
+          <t>-32.877664,-71.231555</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>100.8</v>
+        <v>101.2</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>118052</v>
+        <v>119361.7</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>231</v>
+        <v>136.3</v>
       </c>
     </row>
     <row r="75">
@@ -26027,31 +28049,31 @@
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:15:59</t>
+          <t>2026/09/24 09:13:37</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>-32.687732,-71.209444</t>
+          <t>-32.892716,-71.233065</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>100.8</v>
+        <v>100.5</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>118053.7</v>
+        <v>119363.4</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>240.4</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="76">
@@ -26061,31 +28083,31 @@
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:16:59</t>
+          <t>2026/09/24 09:14:22</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>-32.67326,-71.212754</t>
+          <t>-32.900753,-71.242342</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>98.3</v>
+        <v>100.6</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>118055.3</v>
+        <v>119364.7</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>244.3</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="77">
@@ -26095,31 +28117,31 @@
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:19:59</t>
+          <t>2026/09/24 09:14:37</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>-32.633631,-71.231517</t>
+          <t>-32.901562,-71.24669</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>100.5</v>
+        <v>101.1</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>118060.2</v>
+        <v>119365.1</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>345</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="78">
@@ -26129,31 +28151,31 @@
         </is>
       </c>
       <c r="B78" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:21:00</t>
+          <t>2026/09/24 09:15:37</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>-32.618623,-71.228808</t>
+          <t>-32.906838,-71.263422</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>101.1</v>
+        <v>100.6</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>118061.9</v>
+        <v>119366.8</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>382.9</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="79">
@@ -26163,31 +28185,31 @@
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:22:01</t>
+          <t>2026/09/24 09:16:37</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>-32.618623,-71.228808</t>
+          <t>-32.917581,-71.275583</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>118062.2</v>
+        <v>119368.5</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>382.9</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="80">
@@ -26197,31 +28219,31 @@
         </is>
       </c>
       <c r="B80" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:22:59</t>
+          <t>2026/09/24 09:17:37</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>-32.591626,-71.243924</t>
+          <t>-32.929518,-71.286538</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>101.4</v>
+        <v>100.6</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>118065.2</v>
+        <v>119370.1</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>274.4</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81">
@@ -26231,31 +28253,31 @@
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:23:59</t>
+          <t>2026/09/24 09:17:53</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
-          <t>-32.579517,-71.25286</t>
+          <t>-32.932927,-71.288722</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>98.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>118066.8</v>
+        <v>119370.6</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>187</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -26265,31 +28287,31 @@
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:26:59</t>
+          <t>2026/09/24 09:28:37</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>-32.538069,-71.265541</t>
+          <t>-33.051079,-71.331664</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>100.2</v>
+        <v>108.2</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>118071.8</v>
+        <v>119386.7</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>115.8</v>
+        <v>205.5</v>
       </c>
     </row>
     <row r="83">
@@ -26299,2819 +28321,643 @@
         </is>
       </c>
       <c r="B83" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:27:59</t>
+          <t>2026/09/24 09:29:37</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>-32.523313,-71.262026</t>
+          <t>-33.06071,-71.343696</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>100.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>118073.5</v>
+        <v>119388.2</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>106.3</v>
+        <v>195.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B84" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:28:59</t>
+          <t>2026/09/23 06:44:10</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>-32.508399,-71.259836</t>
+          <t>-32.586372,-71.330742</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>118075.1</v>
+        <v>125648.4</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>80.90000000000001</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B85" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:29:59</t>
+          <t>2026/09/23 06:45:11</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>-32.493383,-71.258738</t>
+          <t>-32.592754,-71.346296</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>100.1</v>
+        <v>95.2</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>118076.8</v>
+        <v>125650</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>67.5</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B86" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 06:30:59</t>
+          <t>2026/09/21 06:48:39</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>-32.479372,-71.257729</t>
+          <t>-32.487837,-71.162004</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>61.4</v>
+        <v>100.7</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>118078.3</v>
+        <v>287164.8</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>54.3</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B87" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:09:43</t>
+          <t>2026/09/21 06:49:39</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>-32.570673,-71.258114</t>
+          <t>-32.482624,-71.176619</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Avenida Humeres, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>100.1</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>118291.5</v>
+        <v>287166.4</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>137</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B88" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:10:43</t>
+          <t>2026/09/21 12:06:37</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>-32.58345,-71.249727</t>
+          <t>-32.573002,-71.291593</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>100.4</v>
+        <v>106.2</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>118293.1</v>
+        <v>287239</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>218.6</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:11:35</t>
+          <t>2026/09/21 12:07:37</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>-32.593706,-71.244038</t>
+          <t>-32.577297,-71.308318</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>s/n, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>97.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>118294.4</v>
+        <v>287240.6</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>287.9</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B90" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:16:43</t>
+          <t>2026/09/22 16:59:18</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>-32.657967,-71.219937</t>
+          <t>-32.402325,-71.369648</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>100.2</v>
+        <v>104.9</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>118302.4</v>
+        <v>287416.6</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>256.2</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B91" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:17:43</t>
+          <t>2026/09/22 16:59:36</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>-32.671887,-71.213259</t>
+          <t>-32.404177,-71.364458</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>100.1</v>
+        <v>103</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>118304.1</v>
+        <v>287417.1</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>247.9</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:18:43</t>
+          <t>2026/09/22 17:00:36</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>-32.686245,-71.209881</t>
+          <t>-32.410297,-71.348035</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Papudo, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>96.7</v>
+        <v>102.4</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>118305.7</v>
+        <v>287418.8</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>240.2</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B93" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:20:43</t>
+          <t>2026/09/22 17:01:36</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
         <is>
-          <t>-32.715016,-71.20483</t>
+          <t>-32.420991,-71.336063</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Papudo, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>100.1</v>
+        <v>92.5</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>118308.9</v>
+        <v>287420.5</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>226.8</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B94" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:21:43</t>
+          <t>2026/09/23 07:57:23</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>-32.729642,-71.201645</t>
+          <t>-32.419658,-71.337312</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Papudo, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
-        <v>100.4</v>
+        <v>105.8</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>118310.6</v>
+        <v>287497.3</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>221.8</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
         </is>
       </c>
       <c r="B95" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:22:43</t>
+          <t>2026/09/23 07:58:22</t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>-32.744294,-71.197665</t>
+          <t>-32.409862,-71.34845</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F95" s="12" t="n">
-        <v>99.7</v>
+        <v>98.3</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>118312.3</v>
+        <v>287498.8</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>215.8</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B96" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:23:43</t>
+          <t>2026/09/22 05:25:50</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>-32.75913,-71.194766</t>
+          <t>-33.16695,-71.530733</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F96" s="12" t="n">
-        <v>100.1</v>
+        <v>100.8</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>118314</v>
+        <v>130988.8</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>210.8</v>
+        <v>341</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B97" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:24:43</t>
+          <t>2026/09/22 05:26:50</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>-32.772231,-71.187796</t>
+          <t>-33.159275,-71.545768</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F97" s="12" t="n">
-        <v>99.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>118315.6</v>
+        <v>130990.4</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>215.3</v>
+        <v>363.5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B98" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:27:26</t>
+          <t>2026/09/24 16:50:40</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>-32.792287,-71.184239</t>
+          <t>-33.173599,-71.518062</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F98" s="12" t="n">
-        <v>100.9</v>
+        <v>101.4</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>118319.6</v>
+        <v>131570.5</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>226</v>
+        <v>342.9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:27:43</t>
+          <t>2026/09/24 16:51:40</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>-32.79032,-71.188361</t>
+          <t>-33.182621,-71.504213</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F99" s="12" t="n">
-        <v>80.5</v>
+        <v>98.2</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>118320.1</v>
+        <v>131572.1</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>223.9</v>
+        <v>344.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GV TOLVA SPGW-29 V OLIVARES</t>
         </is>
       </c>
       <c r="B100" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:28:43</t>
+          <t>2026/09/23 17:35:53</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>-32.798265,-71.202449</t>
+          <t>-32.801057,-71.44118</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F100" s="12" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>118321.7</v>
+        <v>109255.6</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>213.4</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GV TOLVA SPGW-29 V OLIVARES</t>
         </is>
       </c>
       <c r="B101" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>2026/09/15 19:29:43</t>
+          <t>2026/09/23 17:36:53</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>-32.805203,-71.218053</t>
+          <t>-32.810575,-71.441477</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F101" s="12" t="n">
-        <v>100.7</v>
+        <v>35.8</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>118323.4</v>
+        <v>109256.7</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>190.6</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B102" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 19:30:41</t>
-        </is>
-      </c>
-      <c r="D102" s="15" t="inlineStr">
-        <is>
-          <t>-32.818547,-71.223532</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>118325</v>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>194.3</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B103" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 19:30:43</t>
-        </is>
-      </c>
-      <c r="D103" s="15" t="inlineStr">
-        <is>
-          <t>-32.819045,-71.223428</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
-        </is>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>118325.1</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>195.5</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B104" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 19:31:43</t>
-        </is>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>-32.833445,-71.220093</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>118326.8</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>165.5</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 19:32:43</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>-32.842854,-71.223933</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr">
-        <is>
-          <t>s/n, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>118327.8</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>153.9</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B106" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 05:59:27</t>
-        </is>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>-32.857544,-71.224635</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>118346.3</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>147.7</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B107" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:00:28</t>
-        </is>
-      </c>
-      <c r="D107" s="15" t="inlineStr">
-        <is>
-          <t>-32.842336,-71.223315</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>118348</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>161.1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B108" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:01:28</t>
-        </is>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>-32.828071,-71.222005</t>
-        </is>
-      </c>
-      <c r="E108" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G108" s="12" t="n">
-        <v>118349.7</v>
-      </c>
-      <c r="H108" s="12" t="n">
-        <v>170.9</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:02:27</t>
-        </is>
-      </c>
-      <c r="D109" s="15" t="inlineStr">
-        <is>
-          <t>-32.813661,-71.223392</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G109" s="12" t="n">
-        <v>118351.4</v>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>185.8</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B110" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:03:22</t>
-        </is>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>-32.802407,-71.214377</t>
-        </is>
-      </c>
-      <c r="E110" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="G110" s="12" t="n">
-        <v>118352.9</v>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>194.8</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B111" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:03:28</t>
-        </is>
-      </c>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>-32.801726,-71.212789</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F111" s="12" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="G111" s="12" t="n">
-        <v>118353.1</v>
-      </c>
-      <c r="H111" s="12" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C112" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:08:28</t>
-        </is>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>-32.775572,-71.183454</t>
-        </is>
-      </c>
-      <c r="E112" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Calera, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F112" s="12" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="G112" s="12" t="n">
-        <v>118360.4</v>
-      </c>
-      <c r="H112" s="12" t="n">
-        <v>215.6</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B113" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:09:28</t>
-        </is>
-      </c>
-      <c r="D113" s="15" t="inlineStr">
-        <is>
-          <t>-32.763862,-71.193721</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F113" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="G113" s="12" t="n">
-        <v>118362.1</v>
-      </c>
-      <c r="H113" s="12" t="n">
-        <v>212.3</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:10:27</t>
-        </is>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>-32.749228,-71.196422</t>
-        </is>
-      </c>
-      <c r="E114" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F114" s="12" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="G114" s="12" t="n">
-        <v>118363.8</v>
-      </c>
-      <c r="H114" s="12" t="n">
-        <v>215.3</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B115" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="C115" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:11:28</t>
-        </is>
-      </c>
-      <c r="D115" s="15" t="inlineStr">
-        <is>
-          <t>-32.734219,-71.200035</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F115" s="12" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="G115" s="12" t="n">
-        <v>118365.5</v>
-      </c>
-      <c r="H115" s="12" t="n">
-        <v>225.2</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B116" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:12:28</t>
-        </is>
-      </c>
-      <c r="D116" s="15" t="inlineStr">
-        <is>
-          <t>-32.71954,-71.204017</t>
-        </is>
-      </c>
-      <c r="E116" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F116" s="12" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="G116" s="12" t="n">
-        <v>118367.2</v>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>227.1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B117" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:13:28</t>
-        </is>
-      </c>
-      <c r="D117" s="15" t="inlineStr">
-        <is>
-          <t>-32.704554,-71.20613</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F117" s="12" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="G117" s="12" t="n">
-        <v>118368.8</v>
-      </c>
-      <c r="H117" s="12" t="n">
-        <v>232.9</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B118" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="C118" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:14:27</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>-32.689912,-71.208898</t>
-        </is>
-      </c>
-      <c r="E118" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F118" s="12" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="G118" s="12" t="n">
-        <v>118370.5</v>
-      </c>
-      <c r="H118" s="12" t="n">
-        <v>237.8</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B119" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:15:28</t>
-        </is>
-      </c>
-      <c r="D119" s="15" t="inlineStr">
-        <is>
-          <t>-32.674877,-71.212387</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F119" s="12" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="G119" s="12" t="n">
-        <v>118372.2</v>
-      </c>
-      <c r="H119" s="12" t="n">
-        <v>245.5</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B120" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:16:28</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>-32.660707,-71.218272</t>
-        </is>
-      </c>
-      <c r="E120" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F120" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>118373.9</v>
-      </c>
-      <c r="H120" s="12" t="n">
-        <v>253.5</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B121" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C121" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:17:28</t>
-        </is>
-      </c>
-      <c r="D121" s="15" t="inlineStr">
-        <is>
-          <t>-32.647615,-71.227099</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F121" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G121" s="12" t="n">
-        <v>118375.5</v>
-      </c>
-      <c r="H121" s="12" t="n">
-        <v>271.4</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B122" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:18:22</t>
-        </is>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>-32.635433,-71.23198</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F122" s="12" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="G122" s="12" t="n">
-        <v>118377</v>
-      </c>
-      <c r="H122" s="12" t="n">
-        <v>340.4</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B123" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C123" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:18:27</t>
-        </is>
-      </c>
-      <c r="D123" s="15" t="inlineStr">
-        <is>
-          <t>-32.634207,-71.231639</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="n">
-        <v>100.4</v>
-      </c>
-      <c r="G123" s="12" t="n">
-        <v>118377.2</v>
-      </c>
-      <c r="H123" s="12" t="n">
-        <v>345.4</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B124" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C124" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:19:28</t>
-        </is>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>-32.619226,-71.228578</t>
-        </is>
-      </c>
-      <c r="E124" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F124" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="G124" s="12" t="n">
-        <v>118378.9</v>
-      </c>
-      <c r="H124" s="12" t="n">
-        <v>384.9</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C125" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:20:30</t>
-        </is>
-      </c>
-      <c r="D125" s="15" t="inlineStr">
-        <is>
-          <t>-32.619226,-71.228578</t>
-        </is>
-      </c>
-      <c r="E125" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F125" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="G125" s="12" t="n">
-        <v>118379.2</v>
-      </c>
-      <c r="H125" s="12" t="n">
-        <v>384.9</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B126" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:21:28</t>
-        </is>
-      </c>
-      <c r="D126" s="15" t="inlineStr">
-        <is>
-          <t>-32.592028,-71.243677</t>
-        </is>
-      </c>
-      <c r="E126" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F126" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G126" s="12" t="n">
-        <v>118382.2</v>
-      </c>
-      <c r="H126" s="12" t="n">
-        <v>279.6</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B127" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C127" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:22:27</t>
-        </is>
-      </c>
-      <c r="D127" s="15" t="inlineStr">
-        <is>
-          <t>-32.579475,-71.252843</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F127" s="12" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="G127" s="12" t="n">
-        <v>118383.9</v>
-      </c>
-      <c r="H127" s="12" t="n">
-        <v>189.1</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:23:27</t>
-        </is>
-      </c>
-      <c r="D128" s="15" t="inlineStr">
-        <is>
-          <t>-32.565996,-71.260201</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F128" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G128" s="12" t="n">
-        <v>118385.6</v>
-      </c>
-      <c r="H128" s="12" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B129" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:24:28</t>
-        </is>
-      </c>
-      <c r="D129" s="15" t="inlineStr">
-        <is>
-          <t>-32.551997,-71.267618</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F129" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="G129" s="12" t="n">
-        <v>118387.3</v>
-      </c>
-      <c r="H129" s="12" t="n">
-        <v>110.3</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B130" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:25:28</t>
-        </is>
-      </c>
-      <c r="D130" s="15" t="inlineStr">
-        <is>
-          <t>-32.537261,-71.265359</t>
-        </is>
-      </c>
-      <c r="E130" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F130" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="G130" s="12" t="n">
-        <v>118389</v>
-      </c>
-      <c r="H130" s="12" t="n">
-        <v>117.7</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B131" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C131" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:26:28</t>
-        </is>
-      </c>
-      <c r="D131" s="15" t="inlineStr">
-        <is>
-          <t>-32.522467,-71.261832</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F131" s="12" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="G131" s="12" t="n">
-        <v>118390.6</v>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B132" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:27:27</t>
-        </is>
-      </c>
-      <c r="D132" s="15" t="inlineStr">
-        <is>
-          <t>-32.507749,-71.259758</t>
-        </is>
-      </c>
-      <c r="E132" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F132" s="12" t="n">
-        <v>100.4</v>
-      </c>
-      <c r="G132" s="12" t="n">
-        <v>118392.3</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>82.40000000000001</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B133" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:28:28</t>
-        </is>
-      </c>
-      <c r="D133" s="15" t="inlineStr">
-        <is>
-          <t>-32.492431,-71.258674</t>
-        </is>
-      </c>
-      <c r="E133" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F133" s="12" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="G133" s="12" t="n">
-        <v>118394</v>
-      </c>
-      <c r="H133" s="12" t="n">
-        <v>68.7</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B134" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C134" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:29:28</t>
-        </is>
-      </c>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t>-32.477371,-71.257589</t>
-        </is>
-      </c>
-      <c r="E134" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F134" s="12" t="n">
-        <v>100.4</v>
-      </c>
-      <c r="G134" s="12" t="n">
-        <v>118395.7</v>
-      </c>
-      <c r="H134" s="12" t="n">
-        <v>57.7</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B135" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="C135" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:30:28</t>
-        </is>
-      </c>
-      <c r="D135" s="15" t="inlineStr">
-        <is>
-          <t>-32.46313,-71.256571</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F135" s="12" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="G135" s="12" t="n">
-        <v>118397.3</v>
-      </c>
-      <c r="H135" s="12" t="n">
-        <v>62.8</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
-        </is>
-      </c>
-      <c r="B136" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/14 06:55:01</t>
-        </is>
-      </c>
-      <c r="D136" s="15" t="inlineStr">
-        <is>
-          <t>-32.592889,-71.34664</t>
-        </is>
-      </c>
-      <c r="E136" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F136" s="12" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="G136" s="12" t="n">
-        <v>232477.2</v>
-      </c>
-      <c r="H136" s="12" t="n">
-        <v>80.40000000000001</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>GP DONGFENG DF6-RXDL-60</t>
-        </is>
-      </c>
-      <c r="B137" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/14 06:56:01</t>
-        </is>
-      </c>
-      <c r="D137" s="15" t="inlineStr">
-        <is>
-          <t>-32.597798,-71.362752</t>
-        </is>
-      </c>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F137" s="12" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="G137" s="12" t="n">
-        <v>232478.8</v>
-      </c>
-      <c r="H137" s="12" t="n">
-        <v>58.5</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B138" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/14 05:07:37</t>
-        </is>
-      </c>
-      <c r="D138" s="15" t="inlineStr">
-        <is>
-          <t>-33.055616,-71.494675</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F138" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G138" s="12" t="n">
-        <v>124680.1</v>
-      </c>
-      <c r="H138" s="12" t="n">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B139" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/14 05:07:58</t>
-        </is>
-      </c>
-      <c r="D139" s="15" t="inlineStr">
-        <is>
-          <t>-33.06,-71.492156</t>
-        </is>
-      </c>
-      <c r="E139" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Troncal Sur, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F139" s="12" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="G139" s="12" t="n">
-        <v>124680.6</v>
-      </c>
-      <c r="H139" s="12" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C140" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 10:12:35</t>
-        </is>
-      </c>
-      <c r="D140" s="15" t="inlineStr">
-        <is>
-          <t>-32.467605,-71.185352</t>
-        </is>
-      </c>
-      <c r="E140" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-285, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F140" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="G140" s="12" t="n">
-        <v>125272.2</v>
-      </c>
-      <c r="H140" s="12" t="n">
-        <v>83.8</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B141" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C141" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 10:13:11</t>
-        </is>
-      </c>
-      <c r="D141" s="15" t="inlineStr">
-        <is>
-          <t>-32.471502,-71.186986</t>
-        </is>
-      </c>
-      <c r="E141" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F141" s="12" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G141" s="12" t="n">
-        <v>125272.6</v>
-      </c>
-      <c r="H141" s="12" t="n">
-        <v>89.3</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B142" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 05:57:39</t>
-        </is>
-      </c>
-      <c r="D142" s="15" t="inlineStr">
-        <is>
-          <t>-32.486699,-71.146003</t>
-        </is>
-      </c>
-      <c r="E142" s="12" t="inlineStr">
-        <is>
-          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F142" s="12" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="G142" s="12" t="n">
-        <v>286839.9</v>
-      </c>
-      <c r="H142" s="12" t="n">
-        <v>112.4</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B143" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 05:58:39</t>
-        </is>
-      </c>
-      <c r="D143" s="15" t="inlineStr">
-        <is>
-          <t>-32.487748,-71.162813</t>
-        </is>
-      </c>
-      <c r="E143" s="12" t="inlineStr">
-        <is>
-          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F143" s="12" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="G143" s="12" t="n">
-        <v>286841.5</v>
-      </c>
-      <c r="H143" s="12" t="n">
-        <v>99.3</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B144" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C144" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 19:15:53</t>
-        </is>
-      </c>
-      <c r="D144" s="15" t="inlineStr">
-        <is>
-          <t>-32.539971,-71.265971</t>
-        </is>
-      </c>
-      <c r="E144" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F144" s="12" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="G144" s="12" t="n">
-        <v>286898.4</v>
-      </c>
-      <c r="H144" s="12" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B145" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C145" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 19:16:54</t>
-        </is>
-      </c>
-      <c r="D145" s="15" t="inlineStr">
-        <is>
-          <t>-32.525162,-71.262459</t>
-        </is>
-      </c>
-      <c r="E145" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F145" s="12" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="G145" s="12" t="n">
-        <v>286900.1</v>
-      </c>
-      <c r="H145" s="12" t="n">
-        <v>106.1</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B146" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C146" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 19:17:53</t>
-        </is>
-      </c>
-      <c r="D146" s="15" t="inlineStr">
-        <is>
-          <t>-32.511285,-71.25998</t>
-        </is>
-      </c>
-      <c r="E146" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F146" s="12" t="n">
-        <v>100.1</v>
-      </c>
-      <c r="G146" s="12" t="n">
-        <v>286901.6</v>
-      </c>
-      <c r="H146" s="12" t="n">
-        <v>82.8</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B147" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C147" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/15 19:18:53</t>
-        </is>
-      </c>
-      <c r="D147" s="15" t="inlineStr">
-        <is>
-          <t>-32.496929,-71.258982</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F147" s="12" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="G147" s="12" t="n">
-        <v>286903.2</v>
-      </c>
-      <c r="H147" s="12" t="n">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B148" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C148" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:30:42</t>
-        </is>
-      </c>
-      <c r="D148" s="15" t="inlineStr">
-        <is>
-          <t>-32.535383,-71.265062</t>
-        </is>
-      </c>
-      <c r="E148" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F148" s="12" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="G148" s="12" t="n">
-        <v>286974.9</v>
-      </c>
-      <c r="H148" s="12" t="n">
-        <v>111.8</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B149" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C149" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:31:42</t>
-        </is>
-      </c>
-      <c r="D149" s="15" t="inlineStr">
-        <is>
-          <t>-32.550003,-71.268371</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F149" s="12" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="G149" s="12" t="n">
-        <v>286976.5</v>
-      </c>
-      <c r="H149" s="12" t="n">
-        <v>107.8</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B150" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:32:42</t>
-        </is>
-      </c>
-      <c r="D150" s="15" t="inlineStr">
-        <is>
-          <t>-32.562662,-71.262115</t>
-        </is>
-      </c>
-      <c r="E150" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F150" s="12" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="G150" s="12" t="n">
-        <v>286978.1</v>
-      </c>
-      <c r="H150" s="12" t="n">
-        <v>119.5</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B151" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C151" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:38:42</t>
-        </is>
-      </c>
-      <c r="D151" s="15" t="inlineStr">
-        <is>
-          <t>-32.588954,-71.337067</t>
-        </is>
-      </c>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F151" s="12" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="G151" s="12" t="n">
-        <v>286985.9</v>
-      </c>
-      <c r="H151" s="12" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B152" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C152" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/16 06:39:42</t>
-        </is>
-      </c>
-      <c r="D152" s="15" t="inlineStr">
-        <is>
-          <t>-32.594776,-71.351703</t>
-        </is>
-      </c>
-      <c r="E152" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F152" s="12" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="G152" s="12" t="n">
-        <v>286987.4</v>
-      </c>
-      <c r="H152" s="12" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B153" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C153" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 06:30:25</t>
-        </is>
-      </c>
-      <c r="D153" s="15" t="inlineStr">
-        <is>
-          <t>-32.509066,-71.260013</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F153" s="12" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="G153" s="12" t="n">
-        <v>287079.1</v>
-      </c>
-      <c r="H153" s="12" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B154" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C154" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 06:31:25</t>
-        </is>
-      </c>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>-32.52402,-71.262373</t>
-        </is>
-      </c>
-      <c r="E154" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F154" s="12" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="G154" s="12" t="n">
-        <v>287080.7</v>
-      </c>
-      <c r="H154" s="12" t="n">
-        <v>103.9</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B155" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C155" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 06:32:25</t>
-        </is>
-      </c>
-      <c r="D155" s="15" t="inlineStr">
-        <is>
-          <t>-32.538522,-71.265815</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F155" s="12" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="G155" s="12" t="n">
-        <v>287082.4</v>
-      </c>
-      <c r="H155" s="12" t="n">
-        <v>113.5</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B156" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C156" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:13:02</t>
-        </is>
-      </c>
-      <c r="D156" s="15" t="inlineStr">
-        <is>
-          <t>-32.58643,-71.330766</t>
-        </is>
-      </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F156" s="12" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="G156" s="12" t="n">
-        <v>287102.9</v>
-      </c>
-      <c r="H156" s="12" t="n">
-        <v>83.40000000000001</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B157" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C157" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:13:55</t>
-        </is>
-      </c>
-      <c r="D157" s="15" t="inlineStr">
-        <is>
-          <t>-32.58039,-71.316058</t>
-        </is>
-      </c>
-      <c r="E157" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F157" s="12" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="G157" s="12" t="n">
-        <v>287104.5</v>
-      </c>
-      <c r="H157" s="12" t="n">
-        <v>76.2</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B158" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C158" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:14:54</t>
-        </is>
-      </c>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>-32.575505,-71.301152</t>
-        </is>
-      </c>
-      <c r="E158" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F158" s="12" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="G158" s="12" t="n">
-        <v>287106</v>
-      </c>
-      <c r="H158" s="12" t="n">
-        <v>78.8</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B159" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C159" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:20:54</t>
-        </is>
-      </c>
-      <c r="D159" s="15" t="inlineStr">
-        <is>
-          <t>-32.550098,-71.268187</t>
-        </is>
-      </c>
-      <c r="E159" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F159" s="12" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="G159" s="12" t="n">
-        <v>287112.1</v>
-      </c>
-      <c r="H159" s="12" t="n">
-        <v>114.9</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B160" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C160" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:21:54</t>
-        </is>
-      </c>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>-32.535637,-71.264919</t>
-        </is>
-      </c>
-      <c r="E160" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F160" s="12" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="G160" s="12" t="n">
-        <v>287113.7</v>
-      </c>
-      <c r="H160" s="12" t="n">
-        <v>117.1</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B161" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C161" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:22:54</t>
-        </is>
-      </c>
-      <c r="D161" s="15" t="inlineStr">
-        <is>
-          <t>-32.520715,-71.261377</t>
-        </is>
-      </c>
-      <c r="E161" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F161" s="12" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="G161" s="12" t="n">
-        <v>287115.4</v>
-      </c>
-      <c r="H161" s="12" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B162" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C162" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:23:54</t>
-        </is>
-      </c>
-      <c r="D162" s="15" t="inlineStr">
-        <is>
-          <t>-32.50592,-71.2596</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F162" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="G162" s="12" t="n">
-        <v>287117.1</v>
-      </c>
-      <c r="H162" s="12" t="n">
-        <v>81.40000000000001</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B163" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C163" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:24:54</t>
-        </is>
-      </c>
-      <c r="D163" s="15" t="inlineStr">
-        <is>
-          <t>-32.491347,-71.258547</t>
-        </is>
-      </c>
-      <c r="E163" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F163" s="12" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="G163" s="12" t="n">
-        <v>287118.7</v>
-      </c>
-      <c r="H163" s="12" t="n">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B164" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="C164" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:51:54</t>
-        </is>
-      </c>
-      <c r="D164" s="15" t="inlineStr">
-        <is>
-          <t>-32.487695,-71.164224</t>
-        </is>
-      </c>
-      <c r="E164" s="12" t="inlineStr">
-        <is>
-          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F164" s="12" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="G164" s="12" t="n">
-        <v>287137.5</v>
-      </c>
-      <c r="H164" s="12" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B165" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="C165" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/17 19:52:54</t>
-        </is>
-      </c>
-      <c r="D165" s="15" t="inlineStr">
-        <is>
-          <t>-32.487289,-71.147938</t>
-        </is>
-      </c>
-      <c r="E165" s="12" t="inlineStr">
-        <is>
-          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F165" s="12" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="G165" s="12" t="n">
-        <v>287139.1</v>
-      </c>
-      <c r="H165" s="12" t="n">
-        <v>114.7</v>
+        <v>18.2</v>
       </c>
     </row>
   </sheetData>
@@ -29217,76 +29063,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId160"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="default" paperSize="1" scale="100" pageOrder="downThenOver" blackAndWhite="0" draft="0" errors="displayed"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId161"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId97"/>
   </tableParts>
 </worksheet>
 </file>
--- a/INFORME EXCESOS DE VELOCIDAD.xlsx
+++ b/INFORME EXCESOS DE VELOCIDAD.xlsx
@@ -222,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I14" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:I14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SpeedingFleetsSummaryTable_1" displayName="SpeedingFleetsSummaryTable_1" ref="A5:I15" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:I15"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Excesos" dataDxfId="0"/>
@@ -240,8 +240,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O50" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:O50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SpeedingFleetsDetailTable_1" displayName="SpeedingFleetsDetailTable_1" ref="A5:O40" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:O40"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Conductor"/>
@@ -264,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H101" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A5:H101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SpeedingFleetsDataTable_1" displayName="SpeedingFleetsDataTable_1" ref="A5:H76" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A5:H76"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Alias"/>
     <tableColumn id="2" name="Secuencial" dataDxfId="0"/>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -593,7 +593,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/10/04 23:59:59</t>
+          <t>Desde : 2026/07/13 00:00:00 Hasta: 2026/10/10 23:59:59</t>
         </is>
       </c>
     </row>
@@ -651,22 +651,22 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0.004456018518518519</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.0005570023148148149</v>
+        <v>0.0006365740740740741</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>114</v>
+        <v>110.2</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>107.1</v>
+        <v>105.6</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.001076388888888889</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0005381944444444444</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>103.2</v>
+        <v>102.6</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>103.2</v>
+        <v>102.4</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
@@ -709,23 +709,23 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.002881944444444444</v>
+        <v>0.0002662037037037037</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.0004803240740740741</v>
+        <v>0.0002662037037037037</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>103.6</v>
+        <v>101.8</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>101.8</v>
@@ -740,26 +740,26 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.004953703703703704</v>
+        <v>0.001388888888888889</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.0003302430555555556</v>
+        <v>0.0006944444444444445</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>112.4</v>
+        <v>114</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>102.8</v>
+        <v>108.6</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -771,26 +771,26 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.004351851851851852</v>
+        <v>0.002418981481481482</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.0006216898148148148</v>
+        <v>0.0002687731481481481</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>10.2</v>
+        <v>5.2</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>108.2</v>
+        <v>105.4</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>101.6</v>
+        <v>101.8</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>0</v>
@@ -802,26 +802,26 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>GC TSVS-89 M AEDO</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.0007060185185185185</v>
+        <v>0.0003472222222222222</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.0007060185185185185</v>
+        <v>0.0001736111111111111</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>100.3</v>
+        <v>107</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>100.3</v>
+        <v>106.4</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
@@ -833,26 +833,26 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+          <t>GC TM5-RXXG-13 D SILVA</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.003668981481481481</v>
+        <v>0.0007060185185185185</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0.0009172453703703703</v>
+        <v>0.0007060185185185185</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>106.2</v>
+        <v>101.1</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>104</v>
+        <v>101.1</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>0</v>
@@ -864,26 +864,26 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>DONGFENG DF6 SRSR-97</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>0.001388888888888889</v>
+        <v>0.002083333333333333</v>
       </c>
       <c r="D13" s="13" t="n">
         <v>0.0006944444444444445</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>101.4</v>
+        <v>103.1</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>101.1</v>
+        <v>103</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>0</v>
@@ -895,31 +895,62 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>GV TOLVA SPGW-29 V OLIVARES</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.001145833333333333</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.0006944444444444445</v>
+        <v>0.0005729166666666667</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>101.4</v>
+        <v>100.8</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>101.4</v>
+        <v>100.6</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>0.004108796296296296</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>0.0006848032407407407</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -944,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O427"/>
+  <dimension ref="A1:O464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -972,7 +1003,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/21 00:00:00 Hasta: 2026/09/27 23:59:58</t>
+          <t>Desde : 2026/09/28 00:00:00 Hasta: 2026/10/04 23:59:58</t>
         </is>
       </c>
     </row>
@@ -23542,7 +23573,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr"/>
       <c r="C393" t="n">
         <v>1</v>
       </c>
@@ -23601,7 +23631,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr"/>
       <c r="C394" t="n">
         <v>1</v>
       </c>
@@ -23660,7 +23689,6 @@
           <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr"/>
       <c r="C395" t="n">
         <v>1</v>
       </c>
@@ -23719,7 +23747,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr"/>
       <c r="C396" t="n">
         <v>2</v>
       </c>
@@ -23778,7 +23805,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr"/>
       <c r="C397" t="n">
         <v>1</v>
       </c>
@@ -23837,7 +23863,6 @@
           <t>GV PEUGEOT THJY-73 J PONCE</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr"/>
       <c r="C398" t="n">
         <v>2</v>
       </c>
@@ -23896,7 +23921,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr"/>
       <c r="C399" t="n">
         <v>2</v>
       </c>
@@ -23955,7 +23979,6 @@
           <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr"/>
       <c r="C400" t="n">
         <v>3</v>
       </c>
@@ -24014,7 +24037,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr"/>
       <c r="C401" t="n">
         <v>3</v>
       </c>
@@ -24073,7 +24095,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr"/>
       <c r="C402" t="n">
         <v>1</v>
       </c>
@@ -24132,7 +24153,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr"/>
       <c r="C403" t="n">
         <v>1</v>
       </c>
@@ -24191,7 +24211,6 @@
           <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr"/>
       <c r="C404" t="n">
         <v>2</v>
       </c>
@@ -24250,7 +24269,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr"/>
       <c r="C405" t="n">
         <v>2</v>
       </c>
@@ -24309,7 +24327,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr"/>
       <c r="C406" t="n">
         <v>3</v>
       </c>
@@ -24368,7 +24385,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr"/>
       <c r="C407" t="n">
         <v>4</v>
       </c>
@@ -24427,7 +24443,6 @@
           <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr"/>
       <c r="C408" t="n">
         <v>1</v>
       </c>
@@ -24486,7 +24501,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr"/>
       <c r="C409" t="n">
         <v>5</v>
       </c>
@@ -24545,7 +24559,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr"/>
       <c r="C410" t="n">
         <v>6</v>
       </c>
@@ -24604,7 +24617,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr"/>
       <c r="C411" t="n">
         <v>4</v>
       </c>
@@ -24663,7 +24675,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr"/>
       <c r="C412" t="n">
         <v>5</v>
       </c>
@@ -24722,7 +24733,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr"/>
       <c r="C413" t="n">
         <v>6</v>
       </c>
@@ -24781,7 +24791,6 @@
           <t>GV SHDV-50 C CARDENAS</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr"/>
       <c r="C414" t="n">
         <v>7</v>
       </c>
@@ -24840,7 +24849,6 @@
           <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr"/>
       <c r="C415" t="n">
         <v>2</v>
       </c>
@@ -24899,7 +24907,6 @@
           <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr"/>
       <c r="C416" t="n">
         <v>1</v>
       </c>
@@ -24958,7 +24965,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr"/>
       <c r="C417" t="n">
         <v>7</v>
       </c>
@@ -25017,7 +25023,6 @@
           <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr"/>
       <c r="C418" t="n">
         <v>1</v>
       </c>
@@ -25076,7 +25081,6 @@
           <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr"/>
       <c r="C419" t="n">
         <v>2</v>
       </c>
@@ -25135,7 +25139,6 @@
           <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr"/>
       <c r="C420" t="n">
         <v>3</v>
       </c>
@@ -25194,7 +25197,6 @@
           <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr"/>
       <c r="C421" t="n">
         <v>4</v>
       </c>
@@ -25253,7 +25255,6 @@
           <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr"/>
       <c r="C422" t="n">
         <v>5</v>
       </c>
@@ -25312,7 +25313,6 @@
           <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr"/>
       <c r="C423" t="n">
         <v>6</v>
       </c>
@@ -25371,7 +25371,6 @@
           <t>GC TM5-RXXG-13 D SILVA</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr"/>
       <c r="C424" t="n">
         <v>1</v>
       </c>
@@ -25430,7 +25429,6 @@
           <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr"/>
       <c r="C425" t="n">
         <v>2</v>
       </c>
@@ -25489,7 +25487,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr"/>
       <c r="C426" t="n">
         <v>8</v>
       </c>
@@ -25548,7 +25545,6 @@
           <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr"/>
       <c r="C427" t="n">
         <v>9</v>
       </c>
@@ -25600,6 +25596,2189 @@
         <v>0</v>
       </c>
       <c r="O427" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="n">
+        <v>1</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026/10/05 00:01:07</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-33.080709,-71.625683</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2026/10/05 00:01:21</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-33.077483,-71.626567</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J428" s="14" t="n">
+        <v>0.000162037037037037</v>
+      </c>
+      <c r="K428" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L428" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M428" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="N428" t="n">
+        <v>0</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="n">
+        <v>1</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026/10/05 06:29:58</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-32.588071,-71.33492</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2026/10/05 06:30:58</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-32.594433,-71.350521</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J429" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K429" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L429" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="M429" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="N429" t="n">
+        <v>0</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="n">
+        <v>1</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026/10/05 09:37:08</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-33.167725,-71.529255</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2026/10/05 09:38:08</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-33.160147,-71.544105</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J430" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K430" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L430" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M430" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N430" t="n">
+        <v>0</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>GLP ALJIBE SJHW-20</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="n">
+        <v>1</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026/10/05 11:26:37</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-33.183882,-71.502956</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2026/10/05 11:27:37</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-33.174262,-71.516428</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J431" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K431" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L431" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="M431" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>GLP ALJIBE SJHW-20</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="n">
+        <v>2</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2026/10/05 11:28:37</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-33.166268,-71.532009</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>2026/10/05 11:30:37</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-33.147691,-71.559311</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J432" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K432" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L432" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="M432" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="N432" t="n">
+        <v>0</v>
+      </c>
+      <c r="O432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="n">
+        <v>2</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026/10/05 11:57:56</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-33.023815,-71.500426</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>2026/10/05 11:58:22</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-33.029231,-71.499572</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Avenida Rubén Hurtado, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J433" s="14" t="n">
+        <v>0.0003009259259259259</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L433" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="M433" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0</v>
+      </c>
+      <c r="O433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="n">
+        <v>1</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026/10/06 07:00:26</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-33.164084,-71.536636</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>2026/10/06 07:01:28</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-33.171945,-71.521297</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J434" s="14" t="n">
+        <v>0.0007175925925925926</v>
+      </c>
+      <c r="K434" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L434" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="M434" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="N434" t="n">
+        <v>0</v>
+      </c>
+      <c r="O434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="n">
+        <v>2</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026/10/06 19:10:35</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-32.507436,-71.259743</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>2026/10/06 19:11:35</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-32.493432,-71.258752</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J435" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K435" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L435" t="n">
+        <v>108</v>
+      </c>
+      <c r="M435" t="n">
+        <v>108</v>
+      </c>
+      <c r="N435" t="n">
+        <v>0</v>
+      </c>
+      <c r="O435" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="n">
+        <v>1</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026/10/07 08:24:53</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-32.733696,-71.43689</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>2026/10/07 08:25:26</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-32.737105,-71.427879</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J436" s="14" t="n">
+        <v>0.0003819444444444445</v>
+      </c>
+      <c r="K436" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L436" t="n">
+        <v>106</v>
+      </c>
+      <c r="M436" t="n">
+        <v>106</v>
+      </c>
+      <c r="N436" t="n">
+        <v>0</v>
+      </c>
+      <c r="O436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="n">
+        <v>2</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026/10/07 08:41:30</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-32.76553,-71.27129</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2026/10/07 08:43:31</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-32.746741,-71.245094</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J437" s="14" t="n">
+        <v>0.001400462962962963</v>
+      </c>
+      <c r="K437" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L437" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="M437" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="N437" t="n">
+        <v>0</v>
+      </c>
+      <c r="O437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="n">
+        <v>3</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:00:46</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-32.831225,-71.220363</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:01:46</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-32.817379,-71.223587</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J438" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K438" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L438" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="M438" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="N438" t="n">
+        <v>0</v>
+      </c>
+      <c r="O438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="n">
+        <v>4</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:03:46</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-32.797298,-71.200103</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:04:34</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-32.790416,-71.188435</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J439" s="14" t="n">
+        <v>0.0005555555555555556</v>
+      </c>
+      <c r="K439" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L439" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="M439" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="N439" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="n">
+        <v>5</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:05:25</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-32.791154,-71.173638</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Autopista Los Andes, Calera, Quillota, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:05:46</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-32.788311,-71.168747</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>s/n, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J440" s="14" t="n">
+        <v>0.0002430555555555555</v>
+      </c>
+      <c r="K440" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L440" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="M440" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="N440" t="n">
+        <v>0</v>
+      </c>
+      <c r="O440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="n">
+        <v>6</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:07:46</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-32.775891,-71.183129</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>s/n, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:11:37</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-32.72215,-71.202884</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>s/n, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J441" s="14" t="n">
+        <v>0.002673611111111111</v>
+      </c>
+      <c r="K441" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L441" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="M441" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="N441" t="n">
+        <v>0</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="n">
+        <v>7</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:12:46</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-32.73051,-71.219687</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>s/n, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:13:46</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-32.738348,-71.235108</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J442" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K442" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L442" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="M442" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="N442" t="n">
+        <v>0</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="n">
+        <v>8</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:15:44</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-32.758679,-71.259963</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:15:46</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-32.759175,-71.259939</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J443" s="14" t="n">
+        <v>2.314814814814815e-05</v>
+      </c>
+      <c r="K443" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L443" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="M443" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="N443" t="n">
+        <v>0</v>
+      </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="n">
+        <v>9</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:25:07</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-32.751382,-71.339026</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Nogales, Quillota, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:29:47</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-32.735759,-71.431632</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J444" s="14" t="n">
+        <v>0.003240740740740741</v>
+      </c>
+      <c r="K444" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L444" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="M444" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="N444" t="n">
+        <v>0</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>JAC  LYTS-17 G GALEA</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="n">
+        <v>10</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:30:47</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-32.725256,-71.441571</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>2026/10/07 11:34:49</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-32.664895,-71.424325</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Ruta E-30-F, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J445" s="14" t="n">
+        <v>0.002800925925925926</v>
+      </c>
+      <c r="K445" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L445" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="M445" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="N445" t="n">
+        <v>0</v>
+      </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="n">
+        <v>1</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2026/10/07 15:38:06</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-33.15684,-71.550963</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2026/10/07 15:39:06</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-33.163908,-71.537088</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J446" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K446" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L446" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="M446" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="N446" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>GV TDLD-98 J PACHECHO</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="n">
+        <v>2</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2026/10/07 15:40:07</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-33.171869,-71.521476</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>2026/10/07 15:42:07</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-33.191591,-71.497048</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J447" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K447" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L447" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M447" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="N447" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="n">
+        <v>3</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026/10/07 18:58:15</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-32.573786,-71.294389</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>2026/10/07 18:59:15</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-32.570142,-71.280173</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J448" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K448" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L448" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="M448" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="n">
+        <v>4</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2026/10/08 05:52:20</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-32.485613,-71.142126</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>2026/10/08 05:53:20</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-32.48824,-71.157938</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J449" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K449" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L449" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="M449" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="N449" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="n">
+        <v>5</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2026/10/08 06:27:20</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-32.521429,-71.261746</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>2026/10/08 06:29:19</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>-32.55169,-71.267926</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J450" s="14" t="n">
+        <v>0.001377314814814815</v>
+      </c>
+      <c r="K450" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L450" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="M450" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="N450" t="n">
+        <v>0</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="n">
+        <v>6</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>2026/10/08 06:35:20</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-32.580048,-71.315306</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>2026/10/08 06:36:20</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-32.586513,-71.331109</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J451" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K451" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L451" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="M451" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="N451" t="n">
+        <v>0</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="n">
+        <v>7</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>2026/10/08 06:37:20</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-32.592902,-71.346688</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>2026/10/08 06:38:19</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-32.597429,-71.361443</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J452" s="14" t="n">
+        <v>0.0006828703703703704</v>
+      </c>
+      <c r="K452" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L452" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="M452" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="N452" t="n">
+        <v>0</v>
+      </c>
+      <c r="O452" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>GV SHDV-50 C CARDENAS</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="n">
+        <v>2</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2026/10/08 06:50:53</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-33.105271,-71.548569</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>2026/10/08 06:51:04</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-33.107194,-71.550915</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J453" s="14" t="n">
+        <v>0.0001273148148148148</v>
+      </c>
+      <c r="K453" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L453" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="M453" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="N453" t="n">
+        <v>0</v>
+      </c>
+      <c r="O453" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="n">
+        <v>8</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2026/10/08 19:11:14</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-32.5506,-71.26814</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>2026/10/08 19:12:14</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-32.535452,-71.264884</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J454" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K454" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L454" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="M454" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="N454" t="n">
+        <v>0</v>
+      </c>
+      <c r="O454" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="n">
+        <v>9</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2026/10/08 19:14:14</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-32.50658,-71.259659</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>2026/10/08 19:17:14</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-32.463891,-71.256606</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="J455" s="14" t="n">
+        <v>0.002083333333333333</v>
+      </c>
+      <c r="K455" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L455" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="M455" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="N455" t="n">
+        <v>0</v>
+      </c>
+      <c r="O455" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="n">
+        <v>10</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2026/10/09 06:27:07</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-32.503805,-71.259649</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Ruta E-35, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>2026/10/09 06:28:07</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-32.518575,-71.261075</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J456" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K456" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L456" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="M456" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="N456" t="n">
+        <v>0</v>
+      </c>
+      <c r="O456" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="n">
+        <v>11</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2026/10/09 06:29:07</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-32.533922,-71.264711</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>2026/10/09 06:31:07</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-32.563984,-71.261471</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>s/n, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J457" s="14" t="n">
+        <v>0.001388888888888889</v>
+      </c>
+      <c r="K457" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L457" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="M457" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="N457" t="n">
+        <v>0</v>
+      </c>
+      <c r="O457" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="n">
+        <v>12</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2026/10/09 06:36:07</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-32.584277,-71.325672</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>s/n, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>2026/10/09 06:37:07</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-32.590725,-71.341367</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="J458" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K458" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L458" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="M458" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="N458" t="n">
+        <v>0</v>
+      </c>
+      <c r="O458" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>GV PEUGEOT THJY-73 J PONCE</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="n">
+        <v>3</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>2026/10/09 08:41:36</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-33.174397,-71.516168</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Avenida Rubén Hurtado, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>2026/10/09 08:42:36</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-33.1668,-71.531074</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+        </is>
+      </c>
+      <c r="J459" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K459" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L459" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="M459" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="N459" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="n">
+        <v>2</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>2026/10/09 10:22:56</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-33.1063,-71.549463</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>2026/10/09 10:23:15</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-33.107898,-71.553742</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J460" s="14" t="n">
+        <v>0.0002199074074074074</v>
+      </c>
+      <c r="K460" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L460" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="M460" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="N460" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>GLP SKDX-44 V VIAL</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="n">
+        <v>1</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>2026/10/10 06:20:35</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-33.089673,-71.541764</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2026/10/10 06:20:38</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-33.090411,-71.541787</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J461" s="14" t="n">
+        <v>3.472222222222222e-05</v>
+      </c>
+      <c r="K461" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L461" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="M461" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N461" t="n">
+        <v>0</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="n">
+        <v>3</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>2026/10/10 06:24:49</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-33.02854,-71.652535</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>2026/10/10 06:26:35</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-33.032794,-71.629225</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+        </is>
+      </c>
+      <c r="J462" s="14" t="n">
+        <v>0.001226851851851852</v>
+      </c>
+      <c r="K462" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L462" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="M462" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="N462" t="n">
+        <v>0</v>
+      </c>
+      <c r="O462" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="n">
+        <v>13</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>2026/10/10 06:26:35</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-32.539766,-71.26607</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>2026/10/10 06:27:35</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-32.553526,-71.266984</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J463" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K463" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L463" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="M463" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N463" t="n">
+        <v>0</v>
+      </c>
+      <c r="O463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>GC MAXUS PKFF-65 G VICENCIO</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="n">
+        <v>14</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>2026/10/10 19:13:08</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-32.51045,-71.259948</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2026/10/10 19:14:08</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-32.49711,-71.259012</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+        </is>
+      </c>
+      <c r="J464" s="14" t="n">
+        <v>0.0006944444444444445</v>
+      </c>
+      <c r="K464" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L464" t="n">
+        <v>102</v>
+      </c>
+      <c r="M464" t="n">
+        <v>102</v>
+      </c>
+      <c r="N464" t="n">
+        <v>0</v>
+      </c>
+      <c r="O464" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25624,7 +27803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.710625" customWidth="1" style="7" min="1" max="1"/>
@@ -25650,7 +27829,7 @@
     <row r="3" ht="25" customHeight="1" s="8">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Desde : 2026/09/21 00:00:00 Hasta: 2026/09/27 23:59:58</t>
+          <t>Desde : 2026/09/28 00:00:00 Hasta: 2026/10/04 23:59:58</t>
         </is>
       </c>
     </row>
@@ -25707,27 +27886,27 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>2026/09/21 16:30:44</t>
+          <t>2026/09/28 10:15:29</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>-33.064531,-71.582122</t>
+          <t>-33.168001,-71.528768</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>100.8</v>
+        <v>104.4</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>195385.6</v>
+        <v>196571.6</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>135.4</v>
+        <v>344.7</v>
       </c>
     </row>
     <row r="7">
@@ -25741,27 +27920,27 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>2026/09/21 16:31:03</t>
+          <t>2026/09/28 10:16:29</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>-33.068343,-71.57905</t>
+          <t>-33.160178,-71.543995</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F7" s="12" t="n">
-        <v>102.2</v>
+        <v>93.2</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>195386.2</v>
+        <v>196573.2</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>147.5</v>
+        <v>366.7</v>
       </c>
     </row>
     <row r="8">
@@ -25771,16 +27950,16 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2026/09/21 16:31:43</t>
+          <t>2026/09/29 17:17:40</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>-33.073399,-71.569769</t>
+          <t>-33.093247,-71.549279</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -25789,13 +27968,13 @@
         </is>
       </c>
       <c r="F8" s="12" t="n">
-        <v>92.59999999999999</v>
+        <v>101</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>195387.2</v>
+        <v>197088</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>164.1</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9">
@@ -25809,27 +27988,27 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 06:52:22</t>
+          <t>2026/09/29 17:18:40</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>-33.106964,-71.550335</t>
+          <t>-33.08311,-71.560254</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>103.2</v>
+        <v>96.3</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>195486.9</v>
+        <v>197089.6</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>349.7</v>
+        <v>186.9</v>
       </c>
     </row>
     <row r="10">
@@ -25839,31 +28018,31 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 06:52:42</t>
+          <t>2026/09/30 07:10:20</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>-33.108835,-71.556265</t>
+          <t>-33.165496,-71.533858</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>97.3</v>
+        <v>110.2</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>195487.5</v>
+        <v>197141.6</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>347.6</v>
+        <v>349.7</v>
       </c>
     </row>
     <row r="11">
@@ -25877,12 +28056,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 06:58:45</t>
+          <t>2026/09/30 07:11:20</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>-33.174097,-71.517021</t>
+          <t>-33.173279,-71.518683</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -25891,13 +28070,13 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>103</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>195497.1</v>
+        <v>197143.2</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>350.9</v>
+        <v>343.5</v>
       </c>
     </row>
     <row r="12">
@@ -25907,31 +28086,31 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 06:59:45</t>
+          <t>2026/09/30 16:26:24</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>-33.182965,-71.503923</t>
+          <t>-33.235353,-71.460898</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>94.2</v>
+        <v>103.1</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>195498.7</v>
+        <v>197389.8</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>350</v>
+        <v>334.3</v>
       </c>
     </row>
     <row r="13">
@@ -25945,27 +28124,27 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 06:47:44</t>
+          <t>2026/09/30 16:27:24</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>-33.106438,-71.549498</t>
+          <t>-33.223146,-71.469762</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>114</v>
+        <v>94.8</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>195843.1</v>
+        <v>197391.4</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>358.2</v>
+        <v>329.2</v>
       </c>
     </row>
     <row r="14">
@@ -25975,16 +28154,16 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 06:48:23</t>
+          <t>2026/10/01 06:52:59</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>-33.110597,-71.559406</t>
+          <t>-33.105892,-71.548968</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -25993,13 +28172,13 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>95.3</v>
+        <v>103.4</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>195844.2</v>
+        <v>197452.9</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>343.9</v>
+        <v>354.4</v>
       </c>
     </row>
     <row r="15">
@@ -26013,27 +28192,27 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 07:01:26</t>
+          <t>2026/10/01 06:53:13</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>-33.254285,-71.441848</t>
+          <t>-33.107785,-71.552729</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>113</v>
+        <v>106.3</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>195864.9</v>
+        <v>197453.3</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>262.9</v>
+        <v>348.9</v>
       </c>
     </row>
     <row r="16">
@@ -26047,27 +28226,27 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 07:01:53</t>
+          <t>2026/10/01 06:53:41</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>-33.259087,-71.438325</t>
+          <t>-33.111009,-71.559679</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Paso de Nivel Lo Vásquez, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>34.9</v>
+        <v>96.2</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>195865.5</v>
+        <v>197454.1</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>275.6</v>
+        <v>341.8</v>
       </c>
     </row>
     <row r="17">
@@ -26081,27 +28260,27 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 06:55:05</t>
+          <t>2026/10/01 07:02:14</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>-33.170963,-71.523157</t>
+          <t>-33.20296,-71.487041</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>107.3</v>
+        <v>106.6</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>196096.4</v>
+        <v>197467.6</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>347.7</v>
+        <v>391.7</v>
       </c>
     </row>
     <row r="18">
@@ -26115,27 +28294,27 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 06:56:05</t>
+          <t>2026/10/01 07:03:14</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>-33.178557,-71.508373</t>
+          <t>-33.213784,-71.475388</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>92.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>196098</v>
+        <v>197469.2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>350.6</v>
+        <v>344.4</v>
       </c>
     </row>
     <row r="19">
@@ -26149,27 +28328,27 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 16:07:24</t>
+          <t>2026/10/01 16:21:31</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>-33.259735,-71.437511</t>
+          <t>-33.093788,-71.548631</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>107.1</v>
+        <v>108.7</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>196267.7</v>
+        <v>197639.4</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>284.3</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20">
@@ -26183,95 +28362,95 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 16:08:24</t>
+          <t>2026/10/01 16:22:14</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>-33.247305,-71.447136</t>
+          <t>-33.087505,-71.558595</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
+          <t>José Santos Ossa, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>94.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>196269.3</v>
+        <v>197640.6</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>267.1</v>
+        <v>218.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 16:17:24</t>
+          <t>2026/10/02 08:36:19</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>-33.158164,-71.548034</t>
+          <t>-33.172529,-71.520037</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>107.9</v>
+        <v>102.6</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>196283.3</v>
+        <v>31107.6</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>359.6</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>GV SHDV-50 C CARDENAS</t>
+          <t>GV TM5 RXXG-15 E CABANILLA</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 16:18:24</t>
+          <t>2026/10/02 08:37:19</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>-33.148261,-71.559017</t>
+          <t>-33.180557,-71.50586</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>93.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>196284.8</v>
+        <v>31109.2</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>338.8</v>
+        <v>347.2</v>
       </c>
     </row>
     <row r="23">
@@ -26281,31 +28460,31 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 17:41:07</t>
+          <t>2026/10/03 08:18:48</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>-32.986627,-71.500563</t>
+          <t>-33.107431,-71.551712</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>103.2</v>
+        <v>102.2</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>29442.9</v>
+        <v>31351.2</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>132.9</v>
+        <v>352.3</v>
       </c>
     </row>
     <row r="24">
@@ -26315,37 +28494,37 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 17:42:07</t>
+          <t>2026/10/03 08:19:21</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>-32.972873,-71.499375</t>
+          <t>-33.110977,-71.559643</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Ruta 64, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>79</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>29444.4</v>
+        <v>31352</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>171</v>
+        <v>345.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
@@ -26353,12 +28532,12 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 10:17:48</t>
+          <t>2026/09/28 13:42:04</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>-33.103997,-71.548121</t>
+          <t>-33.101625,-71.548022</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
@@ -26367,19 +28546,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>103.2</v>
+        <v>101.8</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>129532.5</v>
+        <v>69483.5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>355.8</v>
+        <v>340.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP TM5 TDKV-89 PAISAJISMO</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
@@ -26387,12 +28566,12 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 10:18:21</t>
+          <t>2026/09/28 13:42:27</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>-33.096468,-71.545796</t>
+          <t>-33.096487,-71.545769</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -26401,13 +28580,13 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>93.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>129533.3</v>
+        <v>69484.10000000001</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>311.8</v>
+        <v>310.6</v>
       </c>
     </row>
     <row r="27">
@@ -26417,31 +28596,31 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 11:04:51</t>
+          <t>2026/09/29 11:40:22</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>-32.74668,-71.418272</t>
+          <t>-33.603372,-71.47727</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 78, San Antonio, San Antonio, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>100.5</v>
+        <v>105.7</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>129586.5</v>
+        <v>130311.2</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>25.4</v>
+        <v>162.7</v>
       </c>
     </row>
     <row r="28">
@@ -26451,31 +28630,31 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 11:05:39</t>
+          <t>2026/09/29 11:41:12</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>-32.736764,-71.417754</t>
+          <t>-33.596098,-71.490241</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 78, San Antonio, San Antonio, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>21.9</v>
+        <v>100.4</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>129587.5</v>
+        <v>130312.7</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>22.6</v>
+        <v>193.1</v>
       </c>
     </row>
     <row r="29">
@@ -26485,31 +28664,31 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 14:27:11</t>
+          <t>2026/09/29 11:41:22</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>-32.697632,-71.434125</t>
+          <t>-33.593699,-71.490824</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 78, San Antonio, San Antonio, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>100.8</v>
+        <v>95.8</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>129611.9</v>
+        <v>130313</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>85.40000000000001</v>
+        <v>207.7</v>
       </c>
     </row>
     <row r="30">
@@ -26519,31 +28698,31 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 14:28:11</t>
+          <t>2026/09/29 11:42:22</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>-32.711743,-71.439001</t>
+          <t>-33.581291,-71.502394</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>s/n, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 78, San Antonio, San Antonio, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>129613.6</v>
+        <v>130314.7</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>53.2</v>
+        <v>221.6</v>
       </c>
     </row>
     <row r="31">
@@ -26553,201 +28732,201 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 14:30:11</t>
+          <t>2026/09/29 11:43:22</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>-32.736397,-71.430255</t>
+          <t>-33.570975,-71.518278</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-20, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 78, Cartagena, San Antonio, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>101.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>129616.9</v>
+        <v>130316.6</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>16.5</v>
+        <v>203.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 14:31:07</t>
+          <t>2026/09/30 11:46:33</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>-32.73887,-71.417684</t>
+          <t>-33.089695,-71.541744</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-190, Puchuncaví, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>129618.1</v>
+        <v>282109.1</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>26.9</v>
+        <v>322.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 15:17:42</t>
+          <t>2026/09/30 11:46:54</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>-33.106519,-71.549636</t>
+          <t>-33.094334,-71.54287</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>101.3</v>
+        <v>80.7</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>129673.6</v>
+        <v>282109.7</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>354.9</v>
+        <v>315.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 15:18:16</t>
+          <t>2026/09/30 13:48:33</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>-33.109626,-71.558333</t>
+          <t>-33.066452,-71.635573</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>89</v>
+        <v>101.4</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>129674.5</v>
+        <v>282142.1</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>354.9</v>
+        <v>429.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 16:03:25</t>
+          <t>2026/09/30 13:49:07</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>-33.225873,-71.408757</t>
+          <t>-33.071629,-71.628251</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>103.6</v>
+        <v>86.8</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>129705.7</v>
+        <v>282143</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>298.1</v>
+        <v>432.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>GV PEUGEOT THJY-73 J PONCE</t>
+          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 16:03:43</t>
+          <t>2026/09/30 13:56:07</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>-33.226252,-71.403608</t>
+          <t>-33.112723,-71.560127</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Ruta F-50, Casablanca, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>97.5</v>
+        <v>101.1</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>129706.2</v>
+        <v>282153</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>297.1</v>
+        <v>338.9</v>
       </c>
     </row>
     <row r="37">
@@ -26757,31 +28936,31 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 07:45:10</t>
+          <t>2026/09/30 13:56:49</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>-33.100187,-71.547878</t>
+          <t>-33.121192,-71.561406</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>105.1</v>
+        <v>26.7</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>278693.6</v>
+        <v>282153.9</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>329.5</v>
+        <v>348.1</v>
       </c>
     </row>
     <row r="38">
@@ -26791,31 +28970,31 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 07:45:36</t>
+          <t>2026/10/01 08:52:29</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>-33.095247,-71.543902</t>
+          <t>-33.094963,-71.543668</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>97.09999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>278694.3</v>
+        <v>282570.6</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>312.9</v>
+        <v>317.7</v>
       </c>
     </row>
     <row r="39">
@@ -26825,31 +29004,31 @@
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 20:35:30</t>
+          <t>2026/10/01 08:52:48</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>-33.07978,-71.626201</t>
+          <t>-33.097684,-71.548109</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>100.6</v>
+        <v>88.3</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>278813.7</v>
+        <v>282571.1</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>459.3</v>
+        <v>326.1</v>
       </c>
     </row>
     <row r="40">
@@ -26859,31 +29038,31 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 20:36:02</t>
+          <t>2026/10/01 10:30:48</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>-33.074449,-71.627144</t>
+          <t>-33.083354,-71.619375</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>11.3</v>
+        <v>101.2</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>278814.3</v>
+        <v>282605.5</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>431.6</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="41">
@@ -26893,16 +29072,16 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:09:48</t>
+          <t>2026/10/01 10:31:18</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>-33.07467,-71.627206</t>
+          <t>-33.089041,-71.615554</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -26911,13 +29090,13 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>102.1</v>
+        <v>86.7</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>278823.6</v>
+        <v>282606.3</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>443.9</v>
+        <v>465.8</v>
       </c>
     </row>
     <row r="42">
@@ -26927,31 +29106,31 @@
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:10:22</t>
+          <t>2026/10/01 10:38:38</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>-33.081773,-71.624192</t>
+          <t>-33.086219,-71.543703</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
         <v>102.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>278824.5</v>
+        <v>282616.6</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>476.9</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="43">
@@ -26961,31 +29140,31 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:10:41</t>
+          <t>2026/10/01 10:39:18</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>-33.083436,-71.619366</t>
+          <t>-33.078192,-71.546987</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>74.5</v>
+        <v>47.1</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>278825</v>
+        <v>282617.5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>478.1</v>
+        <v>315.9</v>
       </c>
     </row>
     <row r="44">
@@ -26995,31 +29174,31 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:12:11</t>
+          <t>2026/10/02 09:08:34</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>-33.093374,-71.603202</t>
+          <t>-32.951403,-71.509712</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>100.3</v>
+        <v>101</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>278827.1</v>
+        <v>283028.9</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>422.4</v>
+        <v>153.6</v>
       </c>
     </row>
     <row r="45">
@@ -27029,31 +29208,31 @@
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:12:28</t>
+          <t>2026/10/02 09:08:47</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>-33.095154,-71.599305</t>
+          <t>-32.954427,-71.509305</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>102.2</v>
+        <v>97</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>278827.5</v>
+        <v>283029.2</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>439.6</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46">
@@ -27063,31 +29242,31 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:12:49</t>
+          <t>2026/10/03 15:58:08</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>-33.094276,-71.592863</t>
+          <t>-33.083555,-71.6193</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>107</v>
+        <v>105.4</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>278828.2</v>
+        <v>283557.6</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>452.9</v>
+        <v>470.3</v>
       </c>
     </row>
     <row r="47">
@@ -27097,31 +29276,31 @@
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:13:50</t>
+          <t>2026/10/03 15:58:18</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>-33.098312,-71.576965</t>
+          <t>-33.08584,-71.618512</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>87.3</v>
+        <v>89.5</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>278829.8</v>
+        <v>283557.9</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>433.6</v>
+        <v>473.3</v>
       </c>
     </row>
     <row r="48">
@@ -27131,1833 +29310,983 @@
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:15:50</t>
+          <t>2026/10/04 23:59:57</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>-33.108176,-71.555779</t>
+          <t>-33.0902,-71.611533</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>101.2</v>
+        <v>100.8</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>278832.7</v>
+        <v>284033.8</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>343.7</v>
+        <v>458.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:16:02</t>
+          <t>2026/09/30 12:19:08</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>-33.109708,-71.554261</t>
+          <t>-33.094687,-71.543221</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>33</v>
+        <v>105.8</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>278832.9</v>
+        <v>152983.6</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>346.8</v>
+        <v>316.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:16:51</t>
+          <t>2026/09/30 12:19:25</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>-33.102198,-71.548</t>
+          <t>-33.097142,-71.547094</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>107.1</v>
+        <v>77.5</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>278834.1</v>
+        <v>152984</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>347.5</v>
+        <v>321.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B51" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:17:15</t>
+          <t>2026/09/30 12:26:39</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>-33.096372,-71.545629</t>
+          <t>-33.080948,-71.625491</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>100.9</v>
+        <v>107</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>278834.7</v>
+        <v>152994</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>318.2</v>
+        <v>468.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GLP SKDX-44 V VIAL</t>
         </is>
       </c>
       <c r="B52" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:17:45</t>
+          <t>2026/09/30 12:26:52</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>-33.090113,-71.541609</t>
+          <t>-33.07768,-71.626619</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>102.1</v>
+        <v>87.5</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>278835.6</v>
+        <v>152994.4</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>329.9</v>
+        <v>455.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TM5-RXXG-13 D SILVA</t>
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:17:51</t>
+          <t>2026/10/02 17:14:31</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>-33.088636,-71.541976</t>
+          <t>-32.841413,-71.075304</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>101</v>
+        <v>101.1</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>278835.8</v>
+        <v>27468.6</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>334.1</v>
+        <v>320.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TM5-RXXG-13 D SILVA</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:18:40</t>
+          <t>2026/10/02 17:15:32</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>-33.07789,-71.54688</t>
+          <t>-32.838415,-71.058687</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>s/n, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>66.8</v>
+        <v>95.7</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>278837.1</v>
+        <v>27470.1</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>322.9</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:20:51</t>
+          <t>2026/09/28 06:32:57</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>-33.056024,-71.529652</t>
+          <t>-32.574246,-71.296456</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>278840.4</v>
+        <v>126180.4</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>267.6</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:21:04</t>
+          <t>2026/09/28 06:33:57</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>-33.052977,-71.529235</t>
+          <t>-32.577993,-71.310394</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>97.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>278840.7</v>
+        <v>126181.8</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>249.1</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:21:51</t>
+          <t>2026/09/28 19:04:41</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>-33.050259,-71.526545</t>
+          <t>-32.560324,-71.263216</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>103.3</v>
+        <v>103.1</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>278841.9</v>
+        <v>126202</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>192.9</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B58" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 21:22:04</t>
+          <t>2026/09/28 19:05:41</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>-33.052978,-71.525812</t>
+          <t>-32.546247,-71.267475</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>77.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>278842.2</v>
+        <v>126203.7</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>171.9</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 22:52:53</t>
+          <t>2026/09/29 19:10:45</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>-33.080648,-71.5467</t>
+          <t>-32.551068,-71.268055</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>s/n, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>100.7</v>
+        <v>102.9</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>278856.2</v>
+        <v>126310.5</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>301.1</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TSVS-89 M AEDO</t>
         </is>
       </c>
       <c r="B60" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 22:53:54</t>
+          <t>2026/09/29 19:11:45</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>-33.094237,-71.542709</t>
+          <t>-32.536671,-71.265216</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>94.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>278857.8</v>
+        <v>126312.1</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>317.5</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 23:00:53</t>
+          <t>2026/10/01 05:23:14</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>-33.080785,-71.625629</t>
+          <t>-33.202935,-71.486925</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>100.6</v>
+        <v>100.4</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>278868.4</v>
+        <v>132413.8</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>463.5</v>
+        <v>391.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>2026/09/22 23:00:55</t>
+          <t>2026/10/01 05:24:14</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>-33.080376,-71.625952</t>
+          <t>-33.191336,-71.497001</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
+          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>97.7</v>
+        <v>99.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>278868.4</v>
+        <v>132415.4</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>463.7</v>
+        <v>356.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 16:22:13</t>
+          <t>2026/10/02 08:35:07</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>-33.067759,-71.633023</t>
+          <t>-32.951726,-71.509423</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>112.4</v>
+        <v>100.8</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>279237.2</v>
+        <v>132657.3</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>435</v>
+        <v>157.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>DONGFENG DF6 SRSR-97</t>
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 16:22:39</t>
+          <t>2026/10/02 08:35:46</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>-33.072648,-71.627581</t>
+          <t>-32.943273,-71.513582</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Camino La Pólvora, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
+          <t>Ruta E-30-F, Concón, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>93.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>279237.9</v>
+        <v>132658.4</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>431.8</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 16:59:32</t>
+          <t>2026/10/02 09:46:19</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>-33.067309,-71.53576</t>
+          <t>-32.839171,-71.113368</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>279259.6</v>
+        <v>9202.9</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>317</v>
+        <v>286.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>2026/09/23 16:59:57</t>
+          <t>2026/10/02 09:47:14</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>-33.06375,-71.530232</t>
+          <t>-32.846,-71.100759</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Ruta Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Hijuelas, Quillota, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>93.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>279260.3</v>
+        <v>9204.299999999999</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>287.9</v>
+        <v>296.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>2026/09/26 05:57:45</t>
+          <t>2026/10/02 10:01:19</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>-33.090501,-71.541783</t>
+          <t>-32.853244,-70.911949</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Viña del Mar, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>101.5</v>
+        <v>101.7</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>280508</v>
+        <v>9222.299999999999</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>323</v>
+        <v>405</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>GLP DF6 SRSL-99 EMERGENCIA</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>2026/09/26 05:58:06</t>
+          <t>2026/10/02 10:02:19</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>-33.094862,-71.543568</t>
+          <t>-32.852206,-70.894789</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Vía Las Palmas, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>91.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>280508.6</v>
+        <v>9223.9</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>315.8</v>
+        <v>419.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 08:59:37</t>
+          <t>2026/10/02 10:03:19</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>-32.739544,-71.198615</t>
+          <t>-32.851113,-70.877393</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>119341.6</v>
+        <v>9225.5</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>227.8</v>
+        <v>435.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B70" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 09:00:37</t>
+          <t>2026/10/02 10:04:19</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>-32.752198,-71.196065</t>
+          <t>-32.853791,-70.86286</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Ruta 5 Norte, Nogales, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:80, VMaxPes:80</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>119343.1</v>
+        <v>9227</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>216.1</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 09:09:37</t>
+          <t>2026/10/02 10:10:19</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>-32.83366,-71.220176</t>
+          <t>-32.915851,-70.811644</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Llaillay, San Felipe, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>119356.7</v>
+        <v>9235.9</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>166.3</v>
+        <v>755</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 09:10:37</t>
+          <t>2026/10/02 10:11:19</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>-32.848271,-71.224416</t>
+          <t>-32.930469,-70.812007</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, La Cruz, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Panamericana Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>100.6</v>
+        <v>95.7</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>119358.4</v>
+        <v>9237.5</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>150.1</v>
+        <v>811</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 09:11:37</t>
+          <t>2026/10/02 10:17:19</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>-32.863138,-71.226828</t>
+          <t>-32.996391,-70.872991</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Panamericana Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>100.3</v>
+        <v>100.6</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>119360.1</v>
+        <v>9247.299999999999</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>138.9</v>
+        <v>724.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 09:12:37</t>
+          <t>2026/10/02 10:18:19</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>-32.877664,-71.231555</t>
+          <t>-33.005228,-70.885492</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>101.2</v>
+        <v>89.8</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>119361.7</v>
+        <v>9248.799999999999</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>136.3</v>
+        <v>721.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 09:13:37</t>
+          <t>2026/10/02 10:29:19</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>-32.892716,-71.233065</t>
+          <t>-33.129061,-70.816603</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Panamericana Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>100.5</v>
+        <v>104</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>119363.4</v>
+        <v>9264.6</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>117.7</v>
+        <v>549.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>GP FOTON G7 TSVS-96</t>
+          <t>GC TM5-VRVJ-20 L SALINAS</t>
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>2026/09/24 09:14:22</t>
+          <t>2026/10/02 10:30:19</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>-32.900753,-71.242342</t>
+          <t>-33.140738,-70.806368</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
+          <t>Ruta 5 Norte, Tiltil, Chacabuco, Región Metropolitana de Santiago. VMaxLiv:120, VMaxPes:100</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>100.6</v>
+        <v>96.5</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>119364.7</v>
+        <v>9266.200000000001</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>110.1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:14:37</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>-32.901562,-71.24669</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>119365.1</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>117.7</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B78" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:15:37</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>-32.906838,-71.263422</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="G78" s="12" t="n">
-        <v>119366.8</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>101.3</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:16:37</t>
-        </is>
-      </c>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>-32.917581,-71.275583</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="G79" s="12" t="n">
-        <v>119368.5</v>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>97.5</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B80" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:17:37</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>-32.929518,-71.286538</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>119370.1</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:17:53</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>-32.932927,-71.288722</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Los Andes, Quillota, Quillota, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="G81" s="12" t="n">
-        <v>119370.6</v>
-      </c>
-      <c r="H81" s="12" t="n">
-        <v>84.59999999999999</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:28:37</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>-33.051079,-71.331664</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>119386.7</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>205.5</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>GP FOTON G7 TSVS-96</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 09:29:37</t>
-        </is>
-      </c>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>-33.06071,-71.343696</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>Autopista Troncal Sur, Villa Alemana, Marga Marga, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="G83" s="12" t="n">
-        <v>119388.2</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>195.3</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/23 06:44:10</t>
-        </is>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>-32.586372,-71.330742</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="G84" s="12" t="n">
-        <v>125648.4</v>
-      </c>
-      <c r="H84" s="12" t="n">
-        <v>71.7</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>GC TSVS-89 M AEDO</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/23 06:45:11</t>
-        </is>
-      </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>-32.592754,-71.346296</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="G85" s="12" t="n">
-        <v>125650</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>75.59999999999999</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/21 06:48:39</t>
-        </is>
-      </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>-32.487837,-71.162004</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t>Avenida El Bosque, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>287164.8</v>
-      </c>
-      <c r="H86" s="12" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B87" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/21 06:49:39</t>
-        </is>
-      </c>
-      <c r="D87" s="15" t="inlineStr">
-        <is>
-          <t>-32.482624,-71.176619</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>Avenida Humeres, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F87" s="12" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="G87" s="12" t="n">
-        <v>287166.4</v>
-      </c>
-      <c r="H87" s="12" t="n">
-        <v>95.5</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B88" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C88" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/21 12:06:37</t>
-        </is>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>-32.573002,-71.291593</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t>Ruta E-462, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:60, VMaxPes:60</t>
-        </is>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>106.2</v>
-      </c>
-      <c r="G88" s="12" t="n">
-        <v>287239</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>81.90000000000001</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B89" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/21 12:07:37</t>
-        </is>
-      </c>
-      <c r="D89" s="15" t="inlineStr">
-        <is>
-          <t>-32.577297,-71.308318</t>
-        </is>
-      </c>
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t>s/n, Zapallar, Petorca, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F89" s="12" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="G89" s="12" t="n">
-        <v>287240.6</v>
-      </c>
-      <c r="H89" s="12" t="n">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/22 16:59:18</t>
-        </is>
-      </c>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>-32.402325,-71.369648</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="G90" s="12" t="n">
-        <v>287416.6</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>83.90000000000001</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B91" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/22 16:59:36</t>
-        </is>
-      </c>
-      <c r="D91" s="15" t="inlineStr">
-        <is>
-          <t>-32.404177,-71.364458</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F91" s="12" t="n">
-        <v>103</v>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>287417.1</v>
-      </c>
-      <c r="H91" s="12" t="n">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B92" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C92" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/22 17:00:36</t>
-        </is>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>-32.410297,-71.348035</t>
-        </is>
-      </c>
-      <c r="E92" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Papudo, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>287418.8</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>83.8</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/22 17:01:36</t>
-        </is>
-      </c>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>-32.420991,-71.336063</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Papudo, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>287420.5</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>40.1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C94" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/23 07:57:23</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>-32.419658,-71.337312</t>
-        </is>
-      </c>
-      <c r="E94" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, Papudo, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>105.8</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>287497.3</v>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>34.4</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="inlineStr">
-        <is>
-          <t>GC MAXUS PKFF-65 G VICENCIO</t>
-        </is>
-      </c>
-      <c r="B95" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C95" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/23 07:58:22</t>
-        </is>
-      </c>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>-32.409862,-71.34845</t>
-        </is>
-      </c>
-      <c r="E95" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 5 Norte, La Ligua, Petorca, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="G95" s="12" t="n">
-        <v>287498.8</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>85.59999999999999</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>DONGFENG DF6 SRSR-97</t>
-        </is>
-      </c>
-      <c r="B96" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/22 05:25:50</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>-33.16695,-71.530733</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>130988.8</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>DONGFENG DF6 SRSR-97</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/22 05:26:50</t>
-        </is>
-      </c>
-      <c r="D97" s="15" t="inlineStr">
-        <is>
-          <t>-33.159275,-71.545768</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:100, VMaxPes:90</t>
-        </is>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>130990.4</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>363.5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>DONGFENG DF6 SRSR-97</t>
-        </is>
-      </c>
-      <c r="B98" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 16:50:40</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>-33.173599,-71.518062</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="G98" s="12" t="n">
-        <v>131570.5</v>
-      </c>
-      <c r="H98" s="12" t="n">
-        <v>342.9</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>DONGFENG DF6 SRSR-97</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/24 16:51:40</t>
-        </is>
-      </c>
-      <c r="D99" s="15" t="inlineStr">
-        <is>
-          <t>-33.182621,-71.504213</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>Ruta 68, Valparaíso, Valparaíso, Región de Valparaíso. VMaxLiv:120, VMaxPes:100</t>
-        </is>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>131572.1</v>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>344.5</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>GV TOLVA SPGW-29 V OLIVARES</t>
-        </is>
-      </c>
-      <c r="B100" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/23 17:35:53</t>
-        </is>
-      </c>
-      <c r="D100" s="15" t="inlineStr">
-        <is>
-          <t>-32.801057,-71.44118</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="inlineStr">
-        <is>
-          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:70, VMaxPes:70</t>
-        </is>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>101.4</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>109255.6</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>29.7</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>GV TOLVA SPGW-29 V OLIVARES</t>
-        </is>
-      </c>
-      <c r="B101" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" s="12" t="inlineStr">
-        <is>
-          <t>2026/09/23 17:36:53</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="inlineStr">
-        <is>
-          <t>-32.810575,-71.441477</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>Ruta F-190, Quintero, Valparaíso, Región de Valparaíso. VMaxLiv:50, VMaxPes:50</t>
-        </is>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>109256.7</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>18.2</v>
+        <v>554.7</v>
       </c>
     </row>
   </sheetData>
@@ -29038,37 +30367,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId96"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="default" paperSize="1" scale="100" pageOrder="downThenOver" blackAndWhite="0" draft="0" errors="displayed"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId97"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId72"/>
   </tableParts>
 </worksheet>
 </file>